--- a/workbooks/ru-vs-mx-1897.xlsx
+++ b/workbooks/ru-vs-mx-1897.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D2AACE-4CA6-407C-9B1F-AB9CA8AD900D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50871EE-937C-4289-B8D8-7B59455E9A96}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="9" xr2:uid="{ADE3E715-68A0-475F-BFDD-EA0E2833FCCA}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="9" xr2:uid="{ADE3E715-68A0-475F-BFDD-EA0E2833FCCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -35,9 +35,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -584,7 +584,7 @@
     <numFmt numFmtId="167" formatCode="0.000000"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2376,7 +2376,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2384,6 +2383,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3158,7 +3158,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7108,7 +7108,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7116,6 +7115,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7908,7 +7908,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -9275,7 +9275,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -10639,7 +10639,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -17809,9 +17809,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -17849,7 +17849,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -17955,7 +17955,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -18097,7 +18097,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -18107,12 +18107,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FE6297-7AA9-4082-887A-7490FB1B1C69}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.15625" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>89</v>
       </c>
@@ -18120,32 +18120,32 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>139</v>
       </c>
@@ -18153,12 +18153,12 @@
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>145</v>
       </c>
@@ -18166,32 +18166,32 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>86</v>
       </c>
@@ -18199,27 +18199,27 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>140</v>
       </c>
@@ -18227,17 +18227,17 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>19</v>
       </c>
@@ -18245,27 +18245,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>112</v>
       </c>
@@ -18273,17 +18273,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>125</v>
       </c>
@@ -18291,22 +18291,22 @@
         <v>126</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>166</v>
       </c>
@@ -18314,12 +18314,12 @@
         <v>167</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>169</v>
       </c>
@@ -18333,15 +18333,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3AA5583-4445-4EF5-9689-A9A4660C684D}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:BB119"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="18" max="18" width="10.3125" customWidth="1"/>
-    <col min="19" max="19" width="12.41796875" customWidth="1"/>
-    <col min="21" max="21" width="10.3125" customWidth="1"/>
-    <col min="22" max="22" width="10.41796875" customWidth="1"/>
+    <col min="18" max="18" width="10.28515625" customWidth="1"/>
+    <col min="19" max="19" width="12.42578125" customWidth="1"/>
+    <col min="21" max="21" width="10.28515625" customWidth="1"/>
+    <col min="22" max="22" width="10.42578125" customWidth="1"/>
+    <col min="27" max="27" width="12.140625" customWidth="1"/>
+    <col min="28" max="28" width="11.140625" customWidth="1"/>
+    <col min="30" max="30" width="10.7109375" customWidth="1"/>
+    <col min="31" max="31" width="11.140625" customWidth="1"/>
+    <col min="33" max="33" width="11.7109375" customWidth="1"/>
+    <col min="34" max="34" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B1" s="6"/>
       <c r="C1" s="32" t="s">
         <v>134</v>
@@ -18401,7 +18407,7 @@
       <c r="BA1" s="32"/>
       <c r="BB1" s="32"/>
     </row>
-    <row r="2" spans="1:54">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="C2" s="32" t="s">
         <v>129</v>
       </c>
@@ -18472,7 +18478,7 @@
       </c>
       <c r="BB2" s="32"/>
     </row>
-    <row r="3" spans="1:54">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="O3" s="6" t="s">
         <v>161</v>
       </c>
@@ -18522,7 +18528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:54">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
@@ -18641,7 +18647,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="5" spans="1:54">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>0</v>
       </c>
@@ -18779,7 +18785,7 @@
         <v>1.0992086535555097</v>
       </c>
     </row>
-    <row r="6" spans="1:54">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>1</v>
       </c>
@@ -18923,7 +18929,7 @@
         <v>1.0815418309455558</v>
       </c>
     </row>
-    <row r="7" spans="1:54">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>2</v>
       </c>
@@ -19069,7 +19075,7 @@
         <v>0.81209939049189861</v>
       </c>
     </row>
-    <row r="8" spans="1:54">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>3</v>
       </c>
@@ -19215,7 +19221,7 @@
         <v>0.50939213218573831</v>
       </c>
     </row>
-    <row r="9" spans="1:54">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>4</v>
       </c>
@@ -19361,7 +19367,7 @@
         <v>0.32773879888163232</v>
       </c>
     </row>
-    <row r="10" spans="1:54">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>5</v>
       </c>
@@ -19507,7 +19513,7 @@
         <v>0.17375823526841613</v>
       </c>
     </row>
-    <row r="11" spans="1:54">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>6</v>
       </c>
@@ -19653,7 +19659,7 @@
         <v>6.3031573144374325E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:54">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>7</v>
       </c>
@@ -19799,7 +19805,7 @@
         <v>2.0988230534600479E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:54">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>8</v>
       </c>
@@ -19945,7 +19951,7 @@
         <v>7.025979663887327E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:54">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>9</v>
       </c>
@@ -20091,7 +20097,7 @@
         <v>2.5682638758206021E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:54">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>10</v>
       </c>
@@ -20237,7 +20243,7 @@
         <v>1.5659405702452441E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:54">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>11</v>
       </c>
@@ -20355,7 +20361,7 @@
       <c r="AR16" s="26"/>
       <c r="AS16" s="26"/>
     </row>
-    <row r="17" spans="1:34">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>12</v>
       </c>
@@ -20394,7 +20400,7 @@
       <c r="AG17" s="24"/>
       <c r="AH17" s="24"/>
     </row>
-    <row r="18" spans="1:34">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>13</v>
       </c>
@@ -20472,7 +20478,7 @@
         <v>0.50373475402895607</v>
       </c>
     </row>
-    <row r="19" spans="1:34">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>14</v>
       </c>
@@ -20515,7 +20521,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="20" spans="1:34">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>15</v>
       </c>
@@ -20546,7 +20552,7 @@
       <c r="X20" s="22"/>
       <c r="Y20" s="22"/>
     </row>
-    <row r="21" spans="1:34">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>16</v>
       </c>
@@ -20577,7 +20583,7 @@
       <c r="X21" s="21"/>
       <c r="Y21" s="21"/>
     </row>
-    <row r="22" spans="1:34">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>17</v>
       </c>
@@ -20608,7 +20614,7 @@
       <c r="X22" s="21"/>
       <c r="Y22" s="21"/>
     </row>
-    <row r="23" spans="1:34">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>18</v>
       </c>
@@ -20639,7 +20645,7 @@
       <c r="X23" s="21"/>
       <c r="Y23" s="21"/>
     </row>
-    <row r="24" spans="1:34">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>19</v>
       </c>
@@ -20670,7 +20676,7 @@
       <c r="X24" s="21"/>
       <c r="Y24" s="21"/>
     </row>
-    <row r="25" spans="1:34">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>20</v>
       </c>
@@ -20701,7 +20707,7 @@
       <c r="X25" s="21"/>
       <c r="Y25" s="21"/>
     </row>
-    <row r="26" spans="1:34">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>21</v>
       </c>
@@ -20732,7 +20738,7 @@
       <c r="X26" s="21"/>
       <c r="Y26" s="21"/>
     </row>
-    <row r="27" spans="1:34">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>22</v>
       </c>
@@ -20763,7 +20769,7 @@
       <c r="X27" s="21"/>
       <c r="Y27" s="21"/>
     </row>
-    <row r="28" spans="1:34">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>23</v>
       </c>
@@ -20794,7 +20800,7 @@
       <c r="X28" s="21"/>
       <c r="Y28" s="21"/>
     </row>
-    <row r="29" spans="1:34">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>24</v>
       </c>
@@ -20825,7 +20831,7 @@
       <c r="X29" s="21"/>
       <c r="Y29" s="21"/>
     </row>
-    <row r="30" spans="1:34">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>25</v>
       </c>
@@ -20856,7 +20862,7 @@
       <c r="X30" s="21"/>
       <c r="Y30" s="21"/>
     </row>
-    <row r="31" spans="1:34">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>26</v>
       </c>
@@ -20887,7 +20893,7 @@
       <c r="X31" s="21"/>
       <c r="Y31" s="21"/>
     </row>
-    <row r="32" spans="1:34">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>27</v>
       </c>
@@ -20918,7 +20924,7 @@
       <c r="X32" s="21"/>
       <c r="Y32" s="21"/>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>28</v>
       </c>
@@ -20949,7 +20955,7 @@
       <c r="X33" s="21"/>
       <c r="Y33" s="21"/>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>29</v>
       </c>
@@ -20980,7 +20986,7 @@
       <c r="X34" s="21"/>
       <c r="Y34" s="21"/>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>30</v>
       </c>
@@ -21011,7 +21017,7 @@
       <c r="X35" s="21"/>
       <c r="Y35" s="21"/>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>31</v>
       </c>
@@ -21042,7 +21048,7 @@
       <c r="X36" s="21"/>
       <c r="Y36" s="21"/>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>32</v>
       </c>
@@ -21073,7 +21079,7 @@
       <c r="X37" s="21"/>
       <c r="Y37" s="21"/>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>33</v>
       </c>
@@ -21104,7 +21110,7 @@
       <c r="X38" s="21"/>
       <c r="Y38" s="21"/>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>34</v>
       </c>
@@ -21135,7 +21141,7 @@
       <c r="X39" s="21"/>
       <c r="Y39" s="21"/>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>35</v>
       </c>
@@ -21166,7 +21172,7 @@
       <c r="X40" s="21"/>
       <c r="Y40" s="21"/>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>36</v>
       </c>
@@ -21197,7 +21203,7 @@
       <c r="X41" s="21"/>
       <c r="Y41" s="21"/>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>37</v>
       </c>
@@ -21228,7 +21234,7 @@
       <c r="X42" s="21"/>
       <c r="Y42" s="21"/>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>38</v>
       </c>
@@ -21259,7 +21265,7 @@
       <c r="X43" s="21"/>
       <c r="Y43" s="21"/>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>39</v>
       </c>
@@ -21290,7 +21296,7 @@
       <c r="X44" s="21"/>
       <c r="Y44" s="21"/>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>40</v>
       </c>
@@ -21321,7 +21327,7 @@
       <c r="X45" s="21"/>
       <c r="Y45" s="21"/>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>41</v>
       </c>
@@ -21352,7 +21358,7 @@
       <c r="X46" s="21"/>
       <c r="Y46" s="21"/>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <v>42</v>
       </c>
@@ -21383,7 +21389,7 @@
       <c r="X47" s="21"/>
       <c r="Y47" s="21"/>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <v>43</v>
       </c>
@@ -21414,7 +21420,7 @@
       <c r="X48" s="21"/>
       <c r="Y48" s="21"/>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="10">
         <v>44</v>
       </c>
@@ -21445,7 +21451,7 @@
       <c r="X49" s="21"/>
       <c r="Y49" s="21"/>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>45</v>
       </c>
@@ -21476,7 +21482,7 @@
       <c r="X50" s="21"/>
       <c r="Y50" s="21"/>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>46</v>
       </c>
@@ -21507,7 +21513,7 @@
       <c r="X51" s="21"/>
       <c r="Y51" s="21"/>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>47</v>
       </c>
@@ -21538,7 +21544,7 @@
       <c r="X52" s="21"/>
       <c r="Y52" s="21"/>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>48</v>
       </c>
@@ -21569,7 +21575,7 @@
       <c r="X53" s="21"/>
       <c r="Y53" s="21"/>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>49</v>
       </c>
@@ -21600,7 +21606,7 @@
       <c r="X54" s="21"/>
       <c r="Y54" s="21"/>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>50</v>
       </c>
@@ -21631,7 +21637,7 @@
       <c r="X55" s="21"/>
       <c r="Y55" s="21"/>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>51</v>
       </c>
@@ -21662,7 +21668,7 @@
       <c r="X56" s="21"/>
       <c r="Y56" s="21"/>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>52</v>
       </c>
@@ -21693,7 +21699,7 @@
       <c r="X57" s="21"/>
       <c r="Y57" s="21"/>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>53</v>
       </c>
@@ -21724,7 +21730,7 @@
       <c r="X58" s="21"/>
       <c r="Y58" s="21"/>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>54</v>
       </c>
@@ -21755,7 +21761,7 @@
       <c r="X59" s="21"/>
       <c r="Y59" s="21"/>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="10">
         <v>55</v>
       </c>
@@ -21786,7 +21792,7 @@
       <c r="X60" s="21"/>
       <c r="Y60" s="21"/>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>56</v>
       </c>
@@ -21817,7 +21823,7 @@
       <c r="X61" s="21"/>
       <c r="Y61" s="21"/>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>57</v>
       </c>
@@ -21848,7 +21854,7 @@
       <c r="X62" s="21"/>
       <c r="Y62" s="21"/>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>58</v>
       </c>
@@ -21879,7 +21885,7 @@
       <c r="X63" s="21"/>
       <c r="Y63" s="21"/>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>59</v>
       </c>
@@ -21910,7 +21916,7 @@
       <c r="X64" s="21"/>
       <c r="Y64" s="21"/>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>60</v>
       </c>
@@ -21941,7 +21947,7 @@
       <c r="X65" s="21"/>
       <c r="Y65" s="21"/>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>61</v>
       </c>
@@ -21972,7 +21978,7 @@
       <c r="X66" s="21"/>
       <c r="Y66" s="21"/>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>62</v>
       </c>
@@ -22003,7 +22009,7 @@
       <c r="X67" s="21"/>
       <c r="Y67" s="21"/>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>63</v>
       </c>
@@ -22034,7 +22040,7 @@
       <c r="X68" s="21"/>
       <c r="Y68" s="21"/>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>64</v>
       </c>
@@ -22065,7 +22071,7 @@
       <c r="X69" s="21"/>
       <c r="Y69" s="21"/>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>65</v>
       </c>
@@ -22096,7 +22102,7 @@
       <c r="X70" s="21"/>
       <c r="Y70" s="21"/>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>66</v>
       </c>
@@ -22127,7 +22133,7 @@
       <c r="X71" s="21"/>
       <c r="Y71" s="21"/>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>67</v>
       </c>
@@ -22158,7 +22164,7 @@
       <c r="X72" s="21"/>
       <c r="Y72" s="21"/>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>68</v>
       </c>
@@ -22189,7 +22195,7 @@
       <c r="X73" s="21"/>
       <c r="Y73" s="21"/>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>69</v>
       </c>
@@ -22220,7 +22226,7 @@
       <c r="X74" s="21"/>
       <c r="Y74" s="21"/>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>70</v>
       </c>
@@ -22251,7 +22257,7 @@
       <c r="X75" s="21"/>
       <c r="Y75" s="21"/>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>71</v>
       </c>
@@ -22282,7 +22288,7 @@
       <c r="X76" s="21"/>
       <c r="Y76" s="21"/>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>72</v>
       </c>
@@ -22313,7 +22319,7 @@
       <c r="X77" s="21"/>
       <c r="Y77" s="21"/>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>73</v>
       </c>
@@ -22344,7 +22350,7 @@
       <c r="X78" s="21"/>
       <c r="Y78" s="21"/>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>74</v>
       </c>
@@ -22375,7 +22381,7 @@
       <c r="X79" s="21"/>
       <c r="Y79" s="21"/>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>75</v>
       </c>
@@ -22406,7 +22412,7 @@
       <c r="X80" s="21"/>
       <c r="Y80" s="21"/>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>76</v>
       </c>
@@ -22437,7 +22443,7 @@
       <c r="X81" s="21"/>
       <c r="Y81" s="21"/>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>77</v>
       </c>
@@ -22468,7 +22474,7 @@
       <c r="X82" s="21"/>
       <c r="Y82" s="21"/>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>78</v>
       </c>
@@ -22499,7 +22505,7 @@
       <c r="X83" s="21"/>
       <c r="Y83" s="21"/>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>79</v>
       </c>
@@ -22530,7 +22536,7 @@
       <c r="X84" s="21"/>
       <c r="Y84" s="21"/>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>80</v>
       </c>
@@ -22561,7 +22567,7 @@
       <c r="X85" s="21"/>
       <c r="Y85" s="21"/>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>81</v>
       </c>
@@ -22592,7 +22598,7 @@
       <c r="X86" s="21"/>
       <c r="Y86" s="21"/>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>82</v>
       </c>
@@ -22623,7 +22629,7 @@
       <c r="X87" s="21"/>
       <c r="Y87" s="21"/>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>83</v>
       </c>
@@ -22654,7 +22660,7 @@
       <c r="X88" s="21"/>
       <c r="Y88" s="21"/>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>84</v>
       </c>
@@ -22685,7 +22691,7 @@
       <c r="X89" s="21"/>
       <c r="Y89" s="21"/>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>85</v>
       </c>
@@ -22716,7 +22722,7 @@
       <c r="X90" s="21"/>
       <c r="Y90" s="21"/>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>86</v>
       </c>
@@ -22747,7 +22753,7 @@
       <c r="X91" s="21"/>
       <c r="Y91" s="21"/>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>87</v>
       </c>
@@ -22778,7 +22784,7 @@
       <c r="X92" s="21"/>
       <c r="Y92" s="21"/>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>88</v>
       </c>
@@ -22809,7 +22815,7 @@
       <c r="X93" s="21"/>
       <c r="Y93" s="21"/>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>89</v>
       </c>
@@ -22840,7 +22846,7 @@
       <c r="X94" s="21"/>
       <c r="Y94" s="21"/>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>90</v>
       </c>
@@ -22871,7 +22877,7 @@
       <c r="X95" s="21"/>
       <c r="Y95" s="21"/>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>91</v>
       </c>
@@ -22902,7 +22908,7 @@
       <c r="X96" s="21"/>
       <c r="Y96" s="21"/>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>92</v>
       </c>
@@ -22933,7 +22939,7 @@
       <c r="X97" s="21"/>
       <c r="Y97" s="21"/>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>93</v>
       </c>
@@ -22964,7 +22970,7 @@
       <c r="X98" s="21"/>
       <c r="Y98" s="21"/>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>94</v>
       </c>
@@ -22995,7 +23001,7 @@
       <c r="X99" s="21"/>
       <c r="Y99" s="21"/>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>95</v>
       </c>
@@ -23026,7 +23032,7 @@
       <c r="X100" s="21"/>
       <c r="Y100" s="21"/>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>96</v>
       </c>
@@ -23057,7 +23063,7 @@
       <c r="X101" s="21"/>
       <c r="Y101" s="21"/>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" s="10">
         <v>97</v>
       </c>
@@ -23088,7 +23094,7 @@
       <c r="X102" s="21"/>
       <c r="Y102" s="21"/>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>98</v>
       </c>
@@ -23119,7 +23125,7 @@
       <c r="X103" s="21"/>
       <c r="Y103" s="21"/>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>99</v>
       </c>
@@ -23150,7 +23156,7 @@
       <c r="X104" s="21"/>
       <c r="Y104" s="21"/>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>100</v>
       </c>
@@ -23181,7 +23187,7 @@
       <c r="X105" s="21"/>
       <c r="Y105" s="21"/>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>101</v>
       </c>
@@ -23212,7 +23218,7 @@
       <c r="X106" s="21"/>
       <c r="Y106" s="21"/>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>102</v>
       </c>
@@ -23243,7 +23249,7 @@
       <c r="X107" s="21"/>
       <c r="Y107" s="21"/>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>103</v>
       </c>
@@ -23274,7 +23280,7 @@
       <c r="X108" s="21"/>
       <c r="Y108" s="21"/>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" s="10">
         <v>104</v>
       </c>
@@ -23305,7 +23311,7 @@
       <c r="X109" s="21"/>
       <c r="Y109" s="21"/>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>105</v>
       </c>
@@ -23336,7 +23342,7 @@
       <c r="X110" s="21"/>
       <c r="Y110" s="21"/>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>106</v>
       </c>
@@ -23367,7 +23373,7 @@
       <c r="X111" s="21"/>
       <c r="Y111" s="21"/>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" s="10">
         <v>107</v>
       </c>
@@ -23398,7 +23404,7 @@
       <c r="X112" s="21"/>
       <c r="Y112" s="21"/>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>108</v>
       </c>
@@ -23429,7 +23435,7 @@
       <c r="X113" s="21"/>
       <c r="Y113" s="21"/>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" s="10">
         <v>109</v>
       </c>
@@ -23460,14 +23466,14 @@
       <c r="X114" s="21"/>
       <c r="Y114" s="21"/>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" s="10"/>
       <c r="F115" s="4"/>
       <c r="G115" s="4"/>
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>116</v>
       </c>
@@ -23504,11 +23510,11 @@
       <c r="X116" s="18"/>
       <c r="Y116" s="18"/>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="F119" s="4"/>
@@ -23518,9 +23524,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="AA1:AH1"/>
-    <mergeCell ref="AJ1:AQ1"/>
     <mergeCell ref="AU1:BB1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="F2:G2"/>
@@ -23538,6 +23541,9 @@
     <mergeCell ref="AG2:AH2"/>
     <mergeCell ref="AJ2:AK2"/>
     <mergeCell ref="AM2:AN2"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="AA1:AH1"/>
+    <mergeCell ref="AJ1:AQ1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23551,12 +23557,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D98FB2-C8D9-4088-84B1-FABE4BAAFA39}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A3:I36"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.41796875" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -23573,7 +23579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>91</v>
       </c>
@@ -23591,7 +23597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -23609,7 +23615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -23627,7 +23633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -23645,7 +23651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
@@ -23663,7 +23669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>109</v>
       </c>
@@ -23681,7 +23687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>110</v>
       </c>
@@ -23699,7 +23705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>92</v>
       </c>
@@ -23717,7 +23723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>93</v>
       </c>
@@ -23735,7 +23741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>94</v>
       </c>
@@ -23753,7 +23759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>95</v>
       </c>
@@ -23771,7 +23777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>96</v>
       </c>
@@ -23789,7 +23795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>97</v>
       </c>
@@ -23809,7 +23815,7 @@
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>98</v>
       </c>
@@ -23827,7 +23833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>99</v>
       </c>
@@ -23845,7 +23851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>100</v>
       </c>
@@ -23863,7 +23869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>101</v>
       </c>
@@ -23881,7 +23887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>102</v>
       </c>
@@ -23899,7 +23905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>103</v>
       </c>
@@ -23917,7 +23923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>104</v>
       </c>
@@ -23935,7 +23941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>105</v>
       </c>
@@ -23953,7 +23959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>106</v>
       </c>
@@ -23971,7 +23977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>107</v>
       </c>
@@ -23989,7 +23995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>108</v>
       </c>
@@ -24007,7 +24013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>118</v>
       </c>
@@ -24025,7 +24031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>11</v>
       </c>
@@ -24043,7 +24049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>17</v>
       </c>
@@ -24061,10 +24067,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="4">
         <f>SUM(B4:B29)-B30</f>
@@ -24079,10 +24085,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>120</v>
       </c>
@@ -24095,10 +24101,10 @@
         <v>6293150</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
     </row>
   </sheetData>
@@ -24110,12 +24116,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81868A5A-2A8A-4DFE-B54B-978D914128E6}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A3:G115"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="23.15625" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" ht="28.8">
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -24129,7 +24135,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -24144,7 +24150,7 @@
         <v>148418.38845550001</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -24159,7 +24165,7 @@
         <v>504141.58268400002</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -24174,7 +24180,7 @@
         <v>938380</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -24189,7 +24195,7 @@
         <v>1320259.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -24204,7 +24210,7 @@
         <v>1718451</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -24219,7 +24225,7 @@
         <v>2062247</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -24234,7 +24240,7 @@
         <v>2408424.8947979999</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -24249,7 +24255,7 @@
         <v>2710054.6795950001</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -24264,7 +24270,7 @@
         <v>2963093.0681820004</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -24279,7 +24285,7 @@
         <v>3156978.0943330005</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -24294,7 +24300,7 @@
         <v>3285521.4110775003</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -24309,7 +24315,7 @@
         <v>3313492.2521325001</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -24324,7 +24330,7 @@
         <v>3403987.9125375003</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -24339,7 +24345,7 @@
         <v>3544050.2009040001</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -24354,7 +24360,7 @@
         <v>3753092.5164105003</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -24369,7 +24375,7 @@
         <v>4043609.0339139998</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -24384,7 +24390,7 @@
         <v>4487741.7788279997</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -24399,7 +24405,7 @@
         <v>4796137.4857899994</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -24414,7 +24420,7 @@
         <v>4996315.8510355009</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -24429,7 +24435,7 @@
         <v>5064204.4860615004</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -24444,7 +24450,7 @@
         <v>4994101.9514699997</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -24459,7 +24465,7 @@
         <v>4693766.1096840007</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
@@ -24474,7 +24480,7 @@
         <v>4654001.5026524998</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>23</v>
       </c>
@@ -24489,7 +24495,7 @@
         <v>4804289.7125144992</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>24</v>
       </c>
@@ -24504,7 +24510,7 @@
         <v>5180287.5264245002</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25</v>
       </c>
@@ -24519,7 +24525,7 @@
         <v>5799582.7765185004</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26</v>
       </c>
@@ -24534,7 +24540,7 @@
         <v>6890150.7608054997</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>27</v>
       </c>
@@ -24549,7 +24555,7 @@
         <v>7458029.812062501</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>28</v>
       </c>
@@ -24564,7 +24570,7 @@
         <v>7598607.5392860007</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>29</v>
       </c>
@@ -24579,7 +24585,7 @@
         <v>7252126.9965094998</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>30</v>
       </c>
@@ -24594,7 +24600,7 @@
         <v>6434176.4525610004</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>31</v>
       </c>
@@ -24609,7 +24615,7 @@
         <v>4928006.5023734998</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>32</v>
       </c>
@@ -24624,7 +24630,7 @@
         <v>4219039.9042025004</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>33</v>
       </c>
@@ -24639,7 +24645,7 @@
         <v>3962429.3410109999</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>34</v>
       </c>
@@ -24654,7 +24660,7 @@
         <v>4187933.6483985004</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>35</v>
       </c>
@@ -24669,7 +24675,7 @@
         <v>4917597.836418001</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>36</v>
       </c>
@@ -24684,7 +24690,7 @@
         <v>6609724.5251209997</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>37</v>
       </c>
@@ -24699,7 +24705,7 @@
         <v>7529801.5464374991</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>38</v>
       </c>
@@ -24714,7 +24720,7 @@
         <v>7841378.8239324996</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>39</v>
       </c>
@@ -24729,7 +24735,7 @@
         <v>7449788.9108264996</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>40</v>
       </c>
@@ -24744,7 +24750,7 @@
         <v>6387883.591914</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>41</v>
       </c>
@@ -24759,7 +24765,7 @@
         <v>4414199.8089654995</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>42</v>
       </c>
@@ -24774,7 +24780,7 @@
         <v>3470807.579835</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>43</v>
       </c>
@@ -24789,7 +24795,7 @@
         <v>3035772.575985</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>44</v>
       </c>
@@ -24804,7 +24810,7 @@
         <v>3103459.4509454998</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>45</v>
       </c>
@@ -24819,7 +24825,7 @@
         <v>3674176.9479415002</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>46</v>
       </c>
@@ -24834,7 +24840,7 @@
         <v>5202589.4151705001</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>47</v>
       </c>
@@ -24849,7 +24855,7 @@
         <v>6019657.9283100003</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>48</v>
       </c>
@@ -24864,7 +24870,7 @@
         <v>6286834.7700359998</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>49</v>
       </c>
@@ -24879,7 +24885,7 @@
         <v>5922088.2277920004</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>50</v>
       </c>
@@ -24894,7 +24900,7 @@
         <v>4966226.0991875008</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>51</v>
       </c>
@@ -24909,7 +24915,7 @@
         <v>3223900.9618140003</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>52</v>
       </c>
@@ -24924,7 +24930,7 @@
         <v>2427925.9459874998</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>53</v>
       </c>
@@ -24939,7 +24945,7 @@
         <v>2073003.8734320002</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>54</v>
       </c>
@@ -24954,7 +24960,7 @@
         <v>2140865.6162040001</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>55</v>
       </c>
@@ -24969,7 +24975,7 @@
         <v>2631204.9925575</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>56</v>
       </c>
@@ -24984,7 +24990,7 @@
         <v>3951940.6652894998</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>57</v>
       </c>
@@ -24999,7 +25005,7 @@
         <v>4702771.3732824996</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>58</v>
       </c>
@@ -25014,7 +25020,7 @@
         <v>5012880.2624159995</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>59</v>
       </c>
@@ -25029,7 +25035,7 @@
         <v>4808838.8045775006</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>60</v>
       </c>
@@ -25044,7 +25050,7 @@
         <v>4116101.6577725005</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>61</v>
       </c>
@@ -25059,7 +25065,7 @@
         <v>2798951.1155595002</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>62</v>
       </c>
@@ -25074,7 +25080,7 @@
         <v>2103863.916375</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>63</v>
       </c>
@@ -25089,7 +25095,7 @@
         <v>1680608.2346620001</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>64</v>
       </c>
@@ -25104,7 +25110,7 @@
         <v>1498388.4679844999</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>65</v>
       </c>
@@ -25119,7 +25125,7 @@
         <v>1524818.824636</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>66</v>
       </c>
@@ -25134,7 +25140,7 @@
         <v>1875512.2431955</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>67</v>
       </c>
@@ -25149,7 +25155,7 @@
         <v>2002169.1185325</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>68</v>
       </c>
@@ -25164,7 +25170,7 @@
         <v>1981221.1491539998</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>69</v>
       </c>
@@ -25179,7 +25185,7 @@
         <v>1799093.2457640001</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>70</v>
       </c>
@@ -25194,7 +25200,7 @@
         <v>1473370.5759689999</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>71</v>
       </c>
@@ -25209,7 +25215,7 @@
         <v>956686.21548500005</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>72</v>
       </c>
@@ -25224,7 +25230,7 @@
         <v>694430.12828249997</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>73</v>
       </c>
@@ -25239,7 +25245,7 @@
         <v>547509.04595100007</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>74</v>
       </c>
@@ -25254,7 +25260,7 @@
         <v>501276.88381199999</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>75</v>
       </c>
@@ -25269,7 +25275,7 @@
         <v>544262.52533500001</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>76</v>
       </c>
@@ -25284,7 +25290,7 @@
         <v>737709.58346849994</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>77</v>
       </c>
@@ -25299,7 +25305,7 @@
         <v>824887.36775249999</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>78</v>
       </c>
@@ -25314,7 +25320,7 @@
         <v>837064.90873250004</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>79</v>
       </c>
@@ -25329,7 +25335,7 @@
         <v>766276.8976425</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>80</v>
       </c>
@@ -25344,7 +25350,7 @@
         <v>621063.87077000004</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>81</v>
       </c>
@@ -25359,7 +25365,7 @@
         <v>381022.00273700006</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>82</v>
       </c>
@@ -25374,7 +25380,7 @@
         <v>260632.0101825</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>83</v>
       </c>
@@ -25389,7 +25395,7 @@
         <v>189619.45786850003</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>84</v>
       </c>
@@ -25404,7 +25410,7 @@
         <v>158546.352224</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>85</v>
       </c>
@@ -25419,7 +25425,7 @@
         <v>159844.611339</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>86</v>
       </c>
@@ -25434,7 +25440,7 @@
         <v>209692.04393349998</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>87</v>
       </c>
@@ -25449,7 +25455,7 @@
         <v>230479.01388750001</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>88</v>
       </c>
@@ -25464,7 +25470,7 @@
         <v>232892.92583400002</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>89</v>
       </c>
@@ -25479,7 +25485,7 @@
         <v>214841.80974599998</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>90</v>
       </c>
@@ -25494,7 +25500,7 @@
         <v>178352.242948</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>91</v>
       </c>
@@ -25509,7 +25515,7 @@
         <v>118221.00668999998</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>92</v>
       </c>
@@ -25524,7 +25530,7 @@
         <v>85945.939417500005</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>93</v>
       </c>
@@ -25539,7 +25545,7 @@
         <v>66007.398473499998</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>94</v>
       </c>
@@ -25554,7 +25560,7 @@
         <v>56533.154012999999</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>95</v>
       </c>
@@ -25569,7 +25575,7 @@
         <v>55736.276697000001</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>96</v>
       </c>
@@ -25584,7 +25590,7 @@
         <v>67715.828398500002</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>97</v>
       </c>
@@ -25599,7 +25605,7 @@
         <v>70919.056454999998</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>98</v>
       </c>
@@ -25614,7 +25620,7 @@
         <v>68579.090468499999</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>99</v>
       </c>
@@ -25629,7 +25635,7 @@
         <v>60367.255556999989</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>100</v>
       </c>
@@ -25644,7 +25650,7 @@
         <v>47131.095663</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>101</v>
       </c>
@@ -25659,7 +25665,7 @@
         <v>27418.664742000001</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>102</v>
       </c>
@@ -25674,7 +25680,7 @@
         <v>17256.233852499998</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>103</v>
       </c>
@@ -25689,7 +25695,7 @@
         <v>10730.117619000001</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>104</v>
       </c>
@@ -25704,7 +25710,7 @@
         <v>6698.4719450000002</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>105</v>
       </c>
@@ -25719,7 +25725,7 @@
         <v>4212.4583325000003</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>106</v>
       </c>
@@ -25734,7 +25740,7 @@
         <v>2698.0035855000001</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>107</v>
       </c>
@@ -25749,7 +25755,7 @@
         <v>1808.4007975</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>108</v>
       </c>
@@ -25764,7 +25770,7 @@
         <v>1336.3730169999999</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>109</v>
       </c>
@@ -25779,7 +25785,7 @@
         <v>1132.0119855</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>119</v>
       </c>
@@ -25806,12 +25812,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8902306-B10F-4126-935C-4C23D644929A}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A3:G115"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="18.83984375" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" ht="39.75" customHeight="1">
+    <row r="3" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -25825,7 +25831,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -25840,7 +25846,7 @@
         <v>226500</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -25855,7 +25861,7 @@
         <v>592500</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -25870,7 +25876,7 @@
         <v>938380</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -25885,7 +25891,7 @@
         <v>1320259.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -25900,7 +25906,7 @@
         <v>1718451</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -25915,7 +25921,7 @@
         <v>2062247</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -25930,7 +25936,7 @@
         <v>2408424.8947979999</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -25945,7 +25951,7 @@
         <v>2710054.6795950001</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -25960,7 +25966,7 @@
         <v>2963093.0681820004</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -25975,7 +25981,7 @@
         <v>3156978.0943330005</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -25990,7 +25996,7 @@
         <v>3285521.4110775003</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -26005,7 +26011,7 @@
         <v>3313492.2521325001</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -26020,7 +26026,7 @@
         <v>3403987.9125375003</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -26035,7 +26041,7 @@
         <v>3544050.2009040001</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -26050,7 +26056,7 @@
         <v>3753092.5164105003</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -26065,7 +26071,7 @@
         <v>4043609.0339139998</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -26080,7 +26086,7 @@
         <v>4487741.7788279997</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -26095,7 +26101,7 @@
         <v>4796137.4857899994</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -26110,7 +26116,7 @@
         <v>4996315.8510355009</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -26125,7 +26131,7 @@
         <v>5064204.4860615004</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -26140,7 +26146,7 @@
         <v>4994101.9514699997</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -26155,7 +26161,7 @@
         <v>4693766.1096840007</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
@@ -26170,7 +26176,7 @@
         <v>4654001.5026524998</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>23</v>
       </c>
@@ -26185,7 +26191,7 @@
         <v>4804289.7125144992</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>24</v>
       </c>
@@ -26200,7 +26206,7 @@
         <v>5180287.5264245002</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25</v>
       </c>
@@ -26215,7 +26221,7 @@
         <v>5799582.7765185004</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26</v>
       </c>
@@ -26230,7 +26236,7 @@
         <v>6890150.7608054997</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>27</v>
       </c>
@@ -26245,7 +26251,7 @@
         <v>7458029.812062501</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>28</v>
       </c>
@@ -26260,7 +26266,7 @@
         <v>7598607.5392860007</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>29</v>
       </c>
@@ -26275,7 +26281,7 @@
         <v>7252126.9965094998</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>30</v>
       </c>
@@ -26290,7 +26296,7 @@
         <v>6434176.4525610004</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>31</v>
       </c>
@@ -26305,7 +26311,7 @@
         <v>4928006.5023734998</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>32</v>
       </c>
@@ -26320,7 +26326,7 @@
         <v>4219039.9042025004</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>33</v>
       </c>
@@ -26335,7 +26341,7 @@
         <v>3962429.3410109999</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>34</v>
       </c>
@@ -26350,7 +26356,7 @@
         <v>4187933.6483985004</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>35</v>
       </c>
@@ -26365,7 +26371,7 @@
         <v>4917597.836418001</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>36</v>
       </c>
@@ -26380,7 +26386,7 @@
         <v>6609724.5251209997</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>37</v>
       </c>
@@ -26395,7 +26401,7 @@
         <v>7529801.5464374991</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>38</v>
       </c>
@@ -26410,7 +26416,7 @@
         <v>7841378.8239324996</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>39</v>
       </c>
@@ -26425,7 +26431,7 @@
         <v>7449788.9108264996</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>40</v>
       </c>
@@ -26440,7 +26446,7 @@
         <v>6387883.591914</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>41</v>
       </c>
@@ -26455,7 +26461,7 @@
         <v>4414199.8089654995</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>42</v>
       </c>
@@ -26470,7 +26476,7 @@
         <v>3470807.579835</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>43</v>
       </c>
@@ -26485,7 +26491,7 @@
         <v>3035772.575985</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>44</v>
       </c>
@@ -26500,7 +26506,7 @@
         <v>3103459.4509454998</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>45</v>
       </c>
@@ -26515,7 +26521,7 @@
         <v>3674176.9479415002</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>46</v>
       </c>
@@ -26530,7 +26536,7 @@
         <v>5202589.4151705001</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>47</v>
       </c>
@@ -26545,7 +26551,7 @@
         <v>6019657.9283100003</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>48</v>
       </c>
@@ -26560,7 +26566,7 @@
         <v>6286834.7700359998</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>49</v>
       </c>
@@ -26575,7 +26581,7 @@
         <v>5922088.2277920004</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>50</v>
       </c>
@@ -26590,7 +26596,7 @@
         <v>4966226.0991875008</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>51</v>
       </c>
@@ -26605,7 +26611,7 @@
         <v>3223900.9618140003</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>52</v>
       </c>
@@ -26620,7 +26626,7 @@
         <v>2427925.9459874998</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>53</v>
       </c>
@@ -26635,7 +26641,7 @@
         <v>2073003.8734320002</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>54</v>
       </c>
@@ -26650,7 +26656,7 @@
         <v>2140865.6162040001</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>55</v>
       </c>
@@ -26665,7 +26671,7 @@
         <v>2631204.9925575</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>56</v>
       </c>
@@ -26680,7 +26686,7 @@
         <v>3951940.6652894998</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>57</v>
       </c>
@@ -26695,7 +26701,7 @@
         <v>4702771.3732824996</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>58</v>
       </c>
@@ -26710,7 +26716,7 @@
         <v>5012880.2624159995</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>59</v>
       </c>
@@ -26725,7 +26731,7 @@
         <v>4808838.8045775006</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>60</v>
       </c>
@@ -26740,7 +26746,7 @@
         <v>4116101.6577725005</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>61</v>
       </c>
@@ -26755,7 +26761,7 @@
         <v>2798951.1155595002</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>62</v>
       </c>
@@ -26770,7 +26776,7 @@
         <v>2103863.916375</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>63</v>
       </c>
@@ -26785,7 +26791,7 @@
         <v>1680608.2346620001</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>64</v>
       </c>
@@ -26800,7 +26806,7 @@
         <v>1498388.4679844999</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>65</v>
       </c>
@@ -26815,7 +26821,7 @@
         <v>1524818.824636</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>66</v>
       </c>
@@ -26830,7 +26836,7 @@
         <v>1875512.2431955</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>67</v>
       </c>
@@ -26845,7 +26851,7 @@
         <v>2002169.1185325</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>68</v>
       </c>
@@ -26860,7 +26866,7 @@
         <v>1981221.1491539998</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>69</v>
       </c>
@@ -26875,7 +26881,7 @@
         <v>1799093.2457640001</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>70</v>
       </c>
@@ -26890,7 +26896,7 @@
         <v>1473370.5759689999</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>71</v>
       </c>
@@ -26905,7 +26911,7 @@
         <v>956686.21548500005</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>72</v>
       </c>
@@ -26920,7 +26926,7 @@
         <v>694430.12828249997</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>73</v>
       </c>
@@ -26935,7 +26941,7 @@
         <v>547509.04595100007</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>74</v>
       </c>
@@ -26950,7 +26956,7 @@
         <v>501276.88381199999</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>75</v>
       </c>
@@ -26965,7 +26971,7 @@
         <v>544262.52533500001</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>76</v>
       </c>
@@ -26980,7 +26986,7 @@
         <v>737709.58346849994</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>77</v>
       </c>
@@ -26995,7 +27001,7 @@
         <v>824887.36775249999</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>78</v>
       </c>
@@ -27010,7 +27016,7 @@
         <v>837064.90873250004</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>79</v>
       </c>
@@ -27025,7 +27031,7 @@
         <v>766276.8976425</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>80</v>
       </c>
@@ -27040,7 +27046,7 @@
         <v>621063.87077000004</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>81</v>
       </c>
@@ -27055,7 +27061,7 @@
         <v>381022.00273700006</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>82</v>
       </c>
@@ -27070,7 +27076,7 @@
         <v>260632.0101825</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>83</v>
       </c>
@@ -27085,7 +27091,7 @@
         <v>189619.45786850003</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>84</v>
       </c>
@@ -27100,7 +27106,7 @@
         <v>158546.352224</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>85</v>
       </c>
@@ -27115,7 +27121,7 @@
         <v>159844.611339</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>86</v>
       </c>
@@ -27130,7 +27136,7 @@
         <v>209692.04393349998</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>87</v>
       </c>
@@ -27145,7 +27151,7 @@
         <v>230479.01388750001</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>88</v>
       </c>
@@ -27160,7 +27166,7 @@
         <v>232892.92583400002</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>89</v>
       </c>
@@ -27175,7 +27181,7 @@
         <v>214841.80974599998</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>90</v>
       </c>
@@ -27190,7 +27196,7 @@
         <v>178352.242948</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>91</v>
       </c>
@@ -27205,7 +27211,7 @@
         <v>118221.00668999998</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>92</v>
       </c>
@@ -27220,7 +27226,7 @@
         <v>85945.939417500005</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>93</v>
       </c>
@@ -27235,7 +27241,7 @@
         <v>66007.398473499998</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>94</v>
       </c>
@@ -27250,7 +27256,7 @@
         <v>56533.154012999999</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>95</v>
       </c>
@@ -27265,7 +27271,7 @@
         <v>55736.276697000001</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>96</v>
       </c>
@@ -27280,7 +27286,7 @@
         <v>67715.828398500002</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>97</v>
       </c>
@@ -27295,7 +27301,7 @@
         <v>70919.056454999998</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>98</v>
       </c>
@@ -27310,7 +27316,7 @@
         <v>68579.090468499999</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>99</v>
       </c>
@@ -27325,7 +27331,7 @@
         <v>60367.255556999989</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>100</v>
       </c>
@@ -27340,7 +27346,7 @@
         <v>47131.095663</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>101</v>
       </c>
@@ -27355,7 +27361,7 @@
         <v>27418.664742000001</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>102</v>
       </c>
@@ -27370,7 +27376,7 @@
         <v>17256.233852499998</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>103</v>
       </c>
@@ -27385,7 +27391,7 @@
         <v>10730.117619000001</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>104</v>
       </c>
@@ -27400,7 +27406,7 @@
         <v>6698.4719450000002</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>105</v>
       </c>
@@ -27415,7 +27421,7 @@
         <v>4212.4583325000003</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>106</v>
       </c>
@@ -27430,7 +27436,7 @@
         <v>2698.0035855000001</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>107</v>
       </c>
@@ -27445,7 +27451,7 @@
         <v>1808.4007975</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>108</v>
       </c>
@@ -27460,7 +27466,7 @@
         <v>1336.3730169999999</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>109</v>
       </c>
@@ -27475,7 +27481,7 @@
         <v>1132.0119855</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>119</v>
       </c>
@@ -27502,22 +27508,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A06B9A9-7CC0-411B-961E-0E444C9F43AF}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A2:L22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.15625" customWidth="1"/>
-    <col min="3" max="3" width="15.578125" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="8" max="8" width="12.83984375" customWidth="1"/>
-    <col min="9" max="9" width="13.578125" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H2" s="29" t="s">
         <v>147</v>
       </c>
       <c r="I2" s="29"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -27540,7 +27546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>0</v>
       </c>
@@ -27566,7 +27572,7 @@
         <v>349709</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -27600,7 +27606,7 @@
         <v>0.53279313816789264</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -27626,7 +27632,7 @@
         <v>150051.70000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -27652,7 +27658,7 @@
         <v>132495.20000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -27678,7 +27684,7 @@
         <v>87370.6</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -27704,7 +27710,7 @@
         <v>55402.2</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -27730,7 +27736,7 @@
         <v>34313.4</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -27756,7 +27762,7 @@
         <v>14517.5</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -27774,10 +27780,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -27794,28 +27800,28 @@
         <v>13582831</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
     </row>
   </sheetData>
@@ -27831,13 +27837,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1373FEDE-1106-466F-9491-B7C4549B767C}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A2:F119"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="21.75" customHeight="1"/>
-    <row r="3" spans="1:6" ht="32.25" customHeight="1">
+    <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -27851,7 +27857,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -27866,7 +27872,7 @@
         <v>356099.20950549998</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -27881,7 +27887,7 @@
         <v>860729.53126950003</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -27896,7 +27902,7 @@
         <v>1252027.81694</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -27911,7 +27917,7 @@
         <v>1532661.955566</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -27926,7 +27932,7 @@
         <v>1743752.3890859997</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -27941,7 +27947,7 @@
         <v>1914577.2237735</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -27956,7 +27962,7 @@
         <v>2070644.8772425</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -27971,7 +27977,7 @@
         <v>2235305.5030200002</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -27986,7 +27992,7 @@
         <v>2430807.1170819998</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -28001,7 +28007,7 @@
         <v>2677057.2231720001</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -28016,7 +28022,7 @@
         <v>3020397.3290609997</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -28031,7 +28037,7 @@
         <v>3341978.656711</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -28046,7 +28052,7 @@
         <v>3661106.4142499999</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -28061,7 +28067,7 @@
         <v>3972502.6472385</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -28076,7 +28082,7 @@
         <v>4273547.5547505002</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -28091,7 +28097,7 @@
         <v>4561505.8791399999</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -28106,7 +28112,7 @@
         <v>4833667.185633</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -28121,7 +28127,7 @@
         <v>5087376.5147625003</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -28136,7 +28142,7 @@
         <v>5320031.9994394993</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -28151,7 +28157,7 @@
         <v>5529364.050171</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -28166,7 +28172,7 @@
         <v>5710543.8966755001</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -28181,7 +28187,7 @@
         <v>5875704.7931664996</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
@@ -28196,7 +28202,7 @@
         <v>6021421.2090450004</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>23</v>
       </c>
@@ -28211,7 +28217,7 @@
         <v>6146976.8485025</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>24</v>
       </c>
@@ -28226,7 +28232,7 @@
         <v>6251432.9945060005</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25</v>
       </c>
@@ -28241,7 +28247,7 @@
         <v>6333922.3505685003</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26</v>
       </c>
@@ -28256,7 +28262,7 @@
         <v>6393640.8157955008</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>27</v>
       </c>
@@ -28271,7 +28277,7 @@
         <v>6429847.795387499</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>28</v>
       </c>
@@ -28286,7 +28292,7 @@
         <v>6441851.6275664996</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>29</v>
       </c>
@@ -28301,7 +28307,7 @@
         <v>6429449.7468570005</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>30</v>
       </c>
@@ -28316,7 +28322,7 @@
         <v>6388194.0240779994</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>31</v>
       </c>
@@ -28331,7 +28337,7 @@
         <v>6340877.1399644995</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>32</v>
       </c>
@@ -28346,7 +28352,7 @@
         <v>6283744.9832300004</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>33</v>
       </c>
@@ -28361,7 +28367,7 @@
         <v>6217489.5963614993</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>34</v>
       </c>
@@ -28376,7 +28382,7 @@
         <v>6142327.6218930008</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>35</v>
       </c>
@@ -28391,7 +28397,7 @@
         <v>6058482.8738775002</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>36</v>
       </c>
@@ -28406,7 +28412,7 @@
         <v>5966167.8316529989</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>37</v>
       </c>
@@ -28421,7 +28427,7 @@
         <v>5865582.2942624995</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>38</v>
       </c>
@@ -28436,7 +28442,7 @@
         <v>5756906.116115001</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>39</v>
       </c>
@@ -28451,7 +28457,7 @@
         <v>5640538.5304160006</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>40</v>
       </c>
@@ -28466,7 +28472,7 @@
         <v>5514542.1890054997</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>41</v>
       </c>
@@ -28481,7 +28487,7 @@
         <v>5391540.2367150001</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>42</v>
       </c>
@@ -28496,7 +28502,7 @@
         <v>5269708.7340275003</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>43</v>
       </c>
@@ -28511,7 +28517,7 @@
         <v>5149608.8537985003</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>44</v>
       </c>
@@ -28526,7 +28532,7 @@
         <v>5031532.1342359995</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>45</v>
       </c>
@@ -28541,7 +28547,7 @@
         <v>4915760.2357954998</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>46</v>
       </c>
@@ -28556,7 +28562,7 @@
         <v>4802555.2450004993</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>47</v>
       </c>
@@ -28571,7 +28577,7 @@
         <v>4692162.2273000004</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>48</v>
       </c>
@@ -28586,7 +28592,7 @@
         <v>4584828.4604360005</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>49</v>
       </c>
@@ -28601,7 +28607,7 @@
         <v>4480412.4230579995</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>50</v>
       </c>
@@ -28616,7 +28622,7 @@
         <v>4382603.064146</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>51</v>
       </c>
@@ -28631,7 +28637,7 @@
         <v>4271165.2143714996</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>52</v>
       </c>
@@ -28646,7 +28652,7 @@
         <v>4149639.1585425003</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>53</v>
       </c>
@@ -28661,7 +28667,7 @@
         <v>4017620.1348425006</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>54</v>
       </c>
@@ -28676,7 +28682,7 @@
         <v>3875119.0986759998</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>55</v>
       </c>
@@ -28691,7 +28697,7 @@
         <v>3722141.9579519997</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>56</v>
       </c>
@@ -28706,7 +28712,7 @@
         <v>3558709.0903434996</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>57</v>
       </c>
@@ -28721,7 +28727,7 @@
         <v>3384854.8833749997</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>58</v>
       </c>
@@ -28736,7 +28742,7 @@
         <v>3200602.2826634999</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>59</v>
       </c>
@@ -28751,7 +28757,7 @@
         <v>3006544.9914780003</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>60</v>
       </c>
@@ -28766,7 +28772,7 @@
         <v>2797605.2052354999</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>61</v>
       </c>
@@ -28781,7 +28787,7 @@
         <v>2604099.8320499999</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>62</v>
       </c>
@@ -28796,7 +28802,7 @@
         <v>2419703.1514375005</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>63</v>
       </c>
@@ -28811,7 +28817,7 @@
         <v>2244229.4544454999</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>64</v>
       </c>
@@ -28826,7 +28832,7 @@
         <v>2076907.1849129999</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>65</v>
       </c>
@@ -28841,7 +28847,7 @@
         <v>1917024.14641</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>66</v>
       </c>
@@ -28856,7 +28862,7 @@
         <v>1763896.738968</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>67</v>
       </c>
@@ -28871,7 +28877,7 @@
         <v>1616862.86919</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>68</v>
       </c>
@@ -28886,7 +28892,7 @@
         <v>1475269.0449615</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>69</v>
       </c>
@@ -28901,7 +28907,7 @@
         <v>1338732.7285509999</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>70</v>
       </c>
@@ -28916,7 +28922,7 @@
         <v>1204296.8558024999</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>71</v>
       </c>
@@ -28931,7 +28937,7 @@
         <v>1085129.2835239999</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>72</v>
       </c>
@@ -28946,7 +28952,7 @@
         <v>977410.17063750012</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>73</v>
       </c>
@@ -28961,7 +28967,7 @@
         <v>880283.906418</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>74</v>
       </c>
@@ -28976,7 +28982,7 @@
         <v>792713.99017800007</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>75</v>
       </c>
@@ -28991,7 +28997,7 @@
         <v>713774.92442949989</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>76</v>
       </c>
@@ -29006,7 +29012,7 @@
         <v>642630.07375649991</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>77</v>
       </c>
@@ -29021,7 +29027,7 @@
         <v>578522.11376999994</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>78</v>
       </c>
@@ -29036,7 +29042,7 @@
         <v>520766.13482850004</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>79</v>
       </c>
@@ -29051,7 +29057,7 @@
         <v>468742.89332850004</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>80</v>
       </c>
@@ -29066,7 +29072,7 @@
         <v>421892.72176799999</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>81</v>
       </c>
@@ -29081,7 +29087,7 @@
         <v>379709.98003999999</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>82</v>
       </c>
@@ -29096,7 +29102,7 @@
         <v>341738.00916750001</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>83</v>
       </c>
@@ -29111,7 +29117,7 @@
         <v>307564.54386849998</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>84</v>
       </c>
@@ -29126,7 +29132,7 @@
         <v>276817.54600500001</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>85</v>
       </c>
@@ -29141,7 +29147,7 @@
         <v>249161.42359350002</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>86</v>
       </c>
@@ -29156,7 +29162,7 @@
         <v>224293.6020435</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>87</v>
       </c>
@@ -29171,7 +29177,7 @@
         <v>201941.41738750003</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>88</v>
       </c>
@@ -29186,7 +29192,7 @@
         <v>181859.30366099998</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>89</v>
       </c>
@@ -29201,7 +29207,7 @@
         <v>163826.250371</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>90</v>
       </c>
@@ -29216,7 +29222,7 @@
         <v>147643.50402699999</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>91</v>
       </c>
@@ -29231,7 +29237,7 @@
         <v>133132.49661450001</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>92</v>
       </c>
@@ -29246,7 +29252,7 @@
         <v>120132.97787999999</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>93</v>
       </c>
@@ -29261,7 +29267,7 @@
         <v>108501.33663049998</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>94</v>
       </c>
@@ -29276,7 +29282,7 @@
         <v>98109.094482</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>95</v>
       </c>
@@ -29291,7 +29297,7 @@
         <v>88841.557404000006</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>96</v>
       </c>
@@ -29306,7 +29312,7 @@
         <v>80596.613272500006</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>97</v>
       </c>
@@ -29321,7 +29327,7 @@
         <v>73283.663310000004</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>98</v>
       </c>
@@ -29336,7 +29342,7 @@
         <v>66822.677966999996</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>99</v>
       </c>
@@ -29351,7 +29357,7 @@
         <v>61143.367795500002</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>100</v>
       </c>
@@ -29366,7 +29372,7 @@
         <v>56184.46248899999</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>101</v>
       </c>
@@ -29381,7 +29387,7 @@
         <v>51893.090969999997</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>102</v>
       </c>
@@ -29396,7 +29402,7 @@
         <v>48224.2572975</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>103</v>
       </c>
@@ -29411,7 +29417,7 @@
         <v>45140.406786</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>104</v>
       </c>
@@ -29426,7 +29432,7 @@
         <v>42611.0816615</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>105</v>
       </c>
@@ -29441,7 +29447,7 @@
         <v>40612.685190999997</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>106</v>
       </c>
@@ -29456,7 +29462,7 @@
         <v>39128.004150000001</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>107</v>
       </c>
@@ -29471,7 +29477,7 @@
         <v>38148.456307500004</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>108</v>
       </c>
@@ -29486,7 +29492,7 @@
         <v>37665.518723000001</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>109</v>
       </c>
@@ -29501,7 +29507,7 @@
         <v>37602.142977000003</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>119</v>
       </c>
@@ -29518,11 +29524,11 @@
         <v>22.311606119984724</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
     </row>
@@ -29536,19 +29542,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D474DA50-C1E5-4EC1-8A12-CB61E6926FFF}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:M129"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="12.68359375" customWidth="1"/>
-    <col min="4" max="4" width="7.15625" customWidth="1"/>
-    <col min="5" max="5" width="8.26171875" customWidth="1"/>
-    <col min="6" max="6" width="11.26171875" customWidth="1"/>
-    <col min="7" max="7" width="16.578125" customWidth="1"/>
-    <col min="8" max="8" width="10.26171875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.15625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" s="30" t="s">
         <v>77</v>
       </c>
@@ -29560,7 +29566,7 @@
       </c>
       <c r="I1" s="30"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -29586,7 +29592,7 @@
       </c>
       <c r="L3" s="30"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -29611,7 +29617,7 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
@@ -29636,7 +29642,7 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
@@ -29661,7 +29667,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -29686,7 +29692,7 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
@@ -29711,7 +29717,7 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
@@ -29736,7 +29742,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>27</v>
       </c>
@@ -29761,7 +29767,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>28</v>
       </c>
@@ -29786,7 +29792,7 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
@@ -29811,7 +29817,7 @@
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>30</v>
       </c>
@@ -29836,7 +29842,7 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>3</v>
       </c>
@@ -29873,7 +29879,7 @@
       </c>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
@@ -29898,7 +29904,7 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>32</v>
       </c>
@@ -29923,7 +29929,7 @@
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
@@ -29948,7 +29954,7 @@
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
@@ -29973,7 +29979,7 @@
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>35</v>
       </c>
@@ -29998,7 +30004,7 @@
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>36</v>
       </c>
@@ -30023,7 +30029,7 @@
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
@@ -30048,7 +30054,7 @@
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -30073,7 +30079,7 @@
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
@@ -30098,7 +30104,7 @@
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -30123,7 +30129,7 @@
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>4</v>
       </c>
@@ -30160,7 +30166,7 @@
       </c>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
@@ -30185,7 +30191,7 @@
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>42</v>
       </c>
@@ -30210,7 +30216,7 @@
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>43</v>
       </c>
@@ -30235,7 +30241,7 @@
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>44</v>
       </c>
@@ -30260,7 +30266,7 @@
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>45</v>
       </c>
@@ -30285,7 +30291,7 @@
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>46</v>
       </c>
@@ -30310,7 +30316,7 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>47</v>
       </c>
@@ -30335,7 +30341,7 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>48</v>
       </c>
@@ -30360,7 +30366,7 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>49</v>
       </c>
@@ -30385,7 +30391,7 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>50</v>
       </c>
@@ -30410,7 +30416,7 @@
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>5</v>
       </c>
@@ -30447,7 +30453,7 @@
       </c>
       <c r="M36" s="4"/>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>51</v>
       </c>
@@ -30472,7 +30478,7 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>52</v>
       </c>
@@ -30497,7 +30503,7 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>53</v>
       </c>
@@ -30522,7 +30528,7 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>54</v>
       </c>
@@ -30547,7 +30553,7 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>55</v>
       </c>
@@ -30572,7 +30578,7 @@
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>56</v>
       </c>
@@ -30597,7 +30603,7 @@
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>57</v>
       </c>
@@ -30622,7 +30628,7 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>58</v>
       </c>
@@ -30647,7 +30653,7 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>59</v>
       </c>
@@ -30672,7 +30678,7 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>60</v>
       </c>
@@ -30697,7 +30703,7 @@
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>6</v>
       </c>
@@ -30734,7 +30740,7 @@
       </c>
       <c r="M47" s="4"/>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>61</v>
       </c>
@@ -30759,7 +30765,7 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>62</v>
       </c>
@@ -30784,7 +30790,7 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>63</v>
       </c>
@@ -30809,7 +30815,7 @@
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>64</v>
       </c>
@@ -30834,7 +30840,7 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>65</v>
       </c>
@@ -30859,7 +30865,7 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>66</v>
       </c>
@@ -30884,7 +30890,7 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>67</v>
       </c>
@@ -30909,7 +30915,7 @@
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>68</v>
       </c>
@@ -30934,7 +30940,7 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>69</v>
       </c>
@@ -30959,7 +30965,7 @@
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>70</v>
       </c>
@@ -30984,7 +30990,7 @@
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>7</v>
       </c>
@@ -31021,7 +31027,7 @@
       </c>
       <c r="M58" s="4"/>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>71</v>
       </c>
@@ -31046,7 +31052,7 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>72</v>
       </c>
@@ -31071,7 +31077,7 @@
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>73</v>
       </c>
@@ -31096,7 +31102,7 @@
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>74</v>
       </c>
@@ -31121,7 +31127,7 @@
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>75</v>
       </c>
@@ -31146,7 +31152,7 @@
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>76</v>
       </c>
@@ -31171,7 +31177,7 @@
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>56</v>
       </c>
@@ -31196,7 +31202,7 @@
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>57</v>
       </c>
@@ -31221,7 +31227,7 @@
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>58</v>
       </c>
@@ -31246,7 +31252,7 @@
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>59</v>
       </c>
@@ -31271,7 +31277,7 @@
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>8</v>
       </c>
@@ -31308,7 +31314,7 @@
       </c>
       <c r="M69" s="4"/>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>60</v>
       </c>
@@ -31333,7 +31339,7 @@
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>61</v>
       </c>
@@ -31358,7 +31364,7 @@
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>62</v>
       </c>
@@ -31383,7 +31389,7 @@
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>63</v>
       </c>
@@ -31408,7 +31414,7 @@
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>64</v>
       </c>
@@ -31433,7 +31439,7 @@
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>65</v>
       </c>
@@ -31458,7 +31464,7 @@
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>66</v>
       </c>
@@ -31483,7 +31489,7 @@
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>67</v>
       </c>
@@ -31508,7 +31514,7 @@
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>68</v>
       </c>
@@ -31533,7 +31539,7 @@
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>69</v>
       </c>
@@ -31558,7 +31564,7 @@
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>9</v>
       </c>
@@ -31595,7 +31601,7 @@
       </c>
       <c r="M80" s="4"/>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>70</v>
       </c>
@@ -31620,7 +31626,7 @@
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>71</v>
       </c>
@@ -31645,7 +31651,7 @@
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>72</v>
       </c>
@@ -31670,7 +31676,7 @@
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>73</v>
       </c>
@@ -31695,7 +31701,7 @@
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>74</v>
       </c>
@@ -31720,7 +31726,7 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>75</v>
       </c>
@@ -31745,7 +31751,7 @@
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>76</v>
       </c>
@@ -31770,7 +31776,7 @@
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>77</v>
       </c>
@@ -31795,7 +31801,7 @@
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>78</v>
       </c>
@@ -31820,7 +31826,7 @@
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>79</v>
       </c>
@@ -31845,7 +31851,7 @@
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>79</v>
       </c>
@@ -31882,7 +31888,7 @@
       </c>
       <c r="M91" s="4"/>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>80</v>
       </c>
@@ -31907,7 +31913,7 @@
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>81</v>
       </c>
@@ -31932,7 +31938,7 @@
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>82</v>
       </c>
@@ -31957,7 +31963,7 @@
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>83</v>
       </c>
@@ -31982,7 +31988,7 @@
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>84</v>
       </c>
@@ -32007,7 +32013,7 @@
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>85</v>
       </c>
@@ -32032,7 +32038,7 @@
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>86</v>
       </c>
@@ -32057,7 +32063,7 @@
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>87</v>
       </c>
@@ -32082,7 +32088,7 @@
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>88</v>
       </c>
@@ -32107,7 +32113,7 @@
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>89</v>
       </c>
@@ -32132,7 +32138,7 @@
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>80</v>
       </c>
@@ -32169,7 +32175,7 @@
       </c>
       <c r="M102" s="4"/>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>90</v>
       </c>
@@ -32194,7 +32200,7 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>91</v>
       </c>
@@ -32219,7 +32225,7 @@
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>92</v>
       </c>
@@ -32244,7 +32250,7 @@
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>93</v>
       </c>
@@ -32269,7 +32275,7 @@
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>94</v>
       </c>
@@ -32294,7 +32300,7 @@
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>95</v>
       </c>
@@ -32319,7 +32325,7 @@
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>96</v>
       </c>
@@ -32344,7 +32350,7 @@
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>97</v>
       </c>
@@ -32369,7 +32375,7 @@
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>98</v>
       </c>
@@ -32394,7 +32400,7 @@
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>99</v>
       </c>
@@ -32419,7 +32425,7 @@
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>81</v>
       </c>
@@ -32456,7 +32462,7 @@
       </c>
       <c r="M113" s="4"/>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>100</v>
       </c>
@@ -32481,7 +32487,7 @@
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>101</v>
       </c>
@@ -32506,7 +32512,7 @@
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>102</v>
       </c>
@@ -32531,7 +32537,7 @@
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>103</v>
       </c>
@@ -32556,7 +32562,7 @@
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>104</v>
       </c>
@@ -32581,7 +32587,7 @@
       <c r="L118" s="4"/>
       <c r="M118" s="4"/>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>105</v>
       </c>
@@ -32606,7 +32612,7 @@
       <c r="L119" s="4"/>
       <c r="M119" s="4"/>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>106</v>
       </c>
@@ -32631,7 +32637,7 @@
       <c r="L120" s="4"/>
       <c r="M120" s="4"/>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>107</v>
       </c>
@@ -32656,7 +32662,7 @@
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>108</v>
       </c>
@@ -32681,7 +32687,7 @@
       <c r="L122" s="4"/>
       <c r="M122" s="4"/>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>109</v>
       </c>
@@ -32706,7 +32712,7 @@
       <c r="L123" s="4"/>
       <c r="M123" s="4"/>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>82</v>
       </c>
@@ -32743,7 +32749,7 @@
       </c>
       <c r="M124" s="4"/>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>83</v>
       </c>
@@ -32768,7 +32774,7 @@
       <c r="L125" s="4"/>
       <c r="M125" s="4"/>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>11</v>
       </c>
@@ -32793,7 +32799,7 @@
       <c r="L126" s="4"/>
       <c r="M126" s="4"/>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>84</v>
       </c>
@@ -32818,7 +32824,7 @@
       <c r="L127" s="4"/>
       <c r="M127" s="4"/>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
@@ -32830,7 +32836,7 @@
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>12</v>
       </c>
@@ -32869,20 +32875,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46408AFA-2B9A-43C2-BB4F-32BDC15D9315}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:V116"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.26171875" customWidth="1"/>
-    <col min="2" max="2" width="10.15625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.15625" customWidth="1"/>
-    <col min="5" max="5" width="9.68359375" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="8" max="8" width="16.26171875" customWidth="1"/>
-    <col min="9" max="9" width="18.83984375" customWidth="1"/>
-    <col min="11" max="11" width="19.41796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.26171875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B1" s="32" t="s">
         <v>117</v>
       </c>
@@ -32903,7 +32909,7 @@
       <c r="P1" s="31"/>
       <c r="Q1" s="31"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
         <v>77</v>
       </c>
@@ -32931,7 +32937,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
@@ -32955,7 +32961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>0</v>
       </c>
@@ -32999,7 +33005,7 @@
         <v>1796267</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>1</v>
       </c>
@@ -33043,7 +33049,7 @@
         <v>4320948</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>2</v>
       </c>
@@ -33087,7 +33093,7 @@
         <v>7278217.5</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>3</v>
       </c>
@@ -33131,7 +33137,7 @@
         <v>10066878.5</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>4</v>
       </c>
@@ -33175,7 +33181,7 @@
         <v>12128265</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>5</v>
       </c>
@@ -33219,7 +33225,7 @@
         <v>13876027</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>6</v>
       </c>
@@ -33263,7 +33269,7 @@
         <v>16120494</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>7</v>
       </c>
@@ -33307,7 +33313,7 @@
         <v>18016500</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>8</v>
       </c>
@@ -33351,7 +33357,7 @@
         <v>20830142.5</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>9</v>
       </c>
@@ -33395,7 +33401,7 @@
         <v>20801494.5</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>10</v>
       </c>
@@ -33439,7 +33445,7 @@
         <v>25404046.5</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>11</v>
       </c>
@@ -33484,7 +33490,7 @@
       </c>
       <c r="V16" s="15"/>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>12</v>
       </c>
@@ -33528,7 +33534,7 @@
         <v>31967175</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>13</v>
       </c>
@@ -33572,7 +33578,7 @@
         <v>28506681</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>14</v>
       </c>
@@ -33616,7 +33622,7 @@
         <v>30058413</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>15</v>
       </c>
@@ -33660,7 +33666,7 @@
         <v>31230624.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>16</v>
       </c>
@@ -33704,7 +33710,7 @@
         <v>34311469.5</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>17</v>
       </c>
@@ -33748,7 +33754,7 @@
         <v>36349057.5</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>18</v>
       </c>
@@ -33792,7 +33798,7 @@
         <v>38629350.5</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>19</v>
       </c>
@@ -33836,7 +33842,7 @@
         <v>34040935.5</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>20</v>
       </c>
@@ -33880,7 +33886,7 @@
         <v>42459723</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>21</v>
       </c>
@@ -33924,7 +33930,7 @@
         <v>30895242</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>22</v>
       </c>
@@ -33968,7 +33974,7 @@
         <v>39357337.5</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>23</v>
       </c>
@@ -34012,7 +34018,7 @@
         <v>38014634</v>
       </c>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>24</v>
       </c>
@@ -34056,7 +34062,7 @@
         <v>34568226</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>25</v>
       </c>
@@ -34100,7 +34106,7 @@
         <v>47633566.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>26</v>
       </c>
@@ -34144,7 +34150,7 @@
         <v>39112277.5</v>
       </c>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>27</v>
       </c>
@@ -34188,7 +34194,7 @@
         <v>42535295</v>
       </c>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>28</v>
       </c>
@@ -34232,7 +34238,7 @@
         <v>45393432</v>
       </c>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>29</v>
       </c>
@@ -34276,7 +34282,7 @@
         <v>27856555</v>
       </c>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>30</v>
       </c>
@@ -34320,7 +34326,7 @@
         <v>74191036.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>31</v>
       </c>
@@ -34364,7 +34370,7 @@
         <v>23358604.5</v>
       </c>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>32</v>
       </c>
@@ -34408,7 +34414,7 @@
         <v>38481820</v>
       </c>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>33</v>
       </c>
@@ -34452,7 +34458,7 @@
         <v>36904002</v>
       </c>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>34</v>
       </c>
@@ -34496,7 +34502,7 @@
         <v>30006237</v>
       </c>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>35</v>
       </c>
@@ -34540,7 +34546,7 @@
         <v>62684409</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>36</v>
       </c>
@@ -34584,7 +34590,7 @@
         <v>40677425</v>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>37</v>
       </c>
@@ -34628,7 +34634,7 @@
         <v>42273675</v>
       </c>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>38</v>
       </c>
@@ -34672,7 +34678,7 @@
         <v>47666811.5</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>39</v>
       </c>
@@ -34716,7 +34722,7 @@
         <v>29246313.5</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>40</v>
       </c>
@@ -34760,7 +34766,7 @@
         <v>85238284.5</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>41</v>
       </c>
@@ -34804,7 +34810,7 @@
         <v>23416499.5</v>
       </c>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <v>42</v>
       </c>
@@ -34848,7 +34854,7 @@
         <v>40651887.5</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <v>43</v>
       </c>
@@ -34892,7 +34898,7 @@
         <v>35213554.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="10">
         <v>44</v>
       </c>
@@ -34936,7 +34942,7 @@
         <v>29809571</v>
       </c>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>45</v>
       </c>
@@ -34980,7 +34986,7 @@
         <v>68794589.5</v>
       </c>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>46</v>
       </c>
@@ -35024,7 +35030,7 @@
         <v>33653584.5</v>
       </c>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>47</v>
       </c>
@@ -35068,7 +35074,7 @@
         <v>33058290</v>
       </c>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>48</v>
       </c>
@@ -35112,7 +35118,7 @@
         <v>41738372.5</v>
       </c>
     </row>
-    <row r="54" spans="1:17">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>49</v>
       </c>
@@ -35156,7 +35162,7 @@
         <v>23197927.5</v>
       </c>
     </row>
-    <row r="55" spans="1:17">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>50</v>
       </c>
@@ -35200,7 +35206,7 @@
         <v>95705529.5</v>
       </c>
     </row>
-    <row r="56" spans="1:17">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>51</v>
       </c>
@@ -35244,7 +35250,7 @@
         <v>18245162.5</v>
       </c>
     </row>
-    <row r="57" spans="1:17">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>52</v>
       </c>
@@ -35288,7 +35294,7 @@
         <v>31964415</v>
       </c>
     </row>
-    <row r="58" spans="1:17">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>53</v>
       </c>
@@ -35332,7 +35338,7 @@
         <v>27448710</v>
       </c>
     </row>
-    <row r="59" spans="1:17">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>54</v>
       </c>
@@ -35376,7 +35382,7 @@
         <v>23594467</v>
       </c>
     </row>
-    <row r="60" spans="1:17">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="10">
         <v>55</v>
       </c>
@@ -35420,7 +35426,7 @@
         <v>62581023</v>
       </c>
     </row>
-    <row r="61" spans="1:17">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>56</v>
       </c>
@@ -35464,7 +35470,7 @@
         <v>30925670.5</v>
       </c>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>57</v>
       </c>
@@ -35508,7 +35514,7 @@
         <v>25349047.5</v>
       </c>
     </row>
-    <row r="63" spans="1:17">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>58</v>
       </c>
@@ -35552,7 +35558,7 @@
         <v>28442290.5</v>
       </c>
     </row>
-    <row r="64" spans="1:17">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>59</v>
       </c>
@@ -35596,7 +35602,7 @@
         <v>15826762</v>
       </c>
     </row>
-    <row r="65" spans="1:17">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>60</v>
       </c>
@@ -35640,7 +35646,7 @@
         <v>96426412.5</v>
       </c>
     </row>
-    <row r="66" spans="1:17">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>61</v>
       </c>
@@ -35684,7 +35690,7 @@
         <v>13570959</v>
       </c>
     </row>
-    <row r="67" spans="1:17">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>62</v>
       </c>
@@ -35728,7 +35734,7 @@
         <v>23397437.5</v>
       </c>
     </row>
-    <row r="68" spans="1:17">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>63</v>
       </c>
@@ -35772,7 +35778,7 @@
         <v>21333015.5</v>
       </c>
     </row>
-    <row r="69" spans="1:17">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>64</v>
       </c>
@@ -35816,7 +35822,7 @@
         <v>15506058</v>
       </c>
     </row>
-    <row r="70" spans="1:17">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>65</v>
       </c>
@@ -35860,7 +35866,7 @@
         <v>49009327</v>
       </c>
     </row>
-    <row r="71" spans="1:17">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>66</v>
       </c>
@@ -35904,7 +35910,7 @@
         <v>16883951</v>
       </c>
     </row>
-    <row r="72" spans="1:17">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>67</v>
       </c>
@@ -35948,7 +35954,7 @@
         <v>18614002.5</v>
       </c>
     </row>
-    <row r="73" spans="1:17">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>68</v>
       </c>
@@ -35992,7 +35998,7 @@
         <v>15265293.5</v>
       </c>
     </row>
-    <row r="74" spans="1:17">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>69</v>
       </c>
@@ -36036,7 +36042,7 @@
         <v>8452103.5</v>
       </c>
     </row>
-    <row r="75" spans="1:17">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>70</v>
       </c>
@@ -36080,7 +36086,7 @@
         <v>63561954</v>
       </c>
     </row>
-    <row r="76" spans="1:17">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>71</v>
       </c>
@@ -36124,7 +36130,7 @@
         <v>6481761</v>
       </c>
     </row>
-    <row r="77" spans="1:17">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>72</v>
       </c>
@@ -36168,7 +36174,7 @@
         <v>11055090</v>
       </c>
     </row>
-    <row r="78" spans="1:17">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>73</v>
       </c>
@@ -36212,7 +36218,7 @@
         <v>8737312.5</v>
       </c>
     </row>
-    <row r="79" spans="1:17">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>74</v>
       </c>
@@ -36256,7 +36262,7 @@
         <v>6519569.5</v>
       </c>
     </row>
-    <row r="80" spans="1:17">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>75</v>
       </c>
@@ -36300,7 +36306,7 @@
         <v>24024402</v>
       </c>
     </row>
-    <row r="81" spans="1:17">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>76</v>
       </c>
@@ -36344,7 +36350,7 @@
         <v>6817603.5</v>
       </c>
     </row>
-    <row r="82" spans="1:17">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>77</v>
       </c>
@@ -36388,7 +36394,7 @@
         <v>5602320</v>
       </c>
     </row>
-    <row r="83" spans="1:17">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>78</v>
       </c>
@@ -36432,7 +36438,7 @@
         <v>6707511</v>
       </c>
     </row>
-    <row r="84" spans="1:17">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>79</v>
       </c>
@@ -36476,7 +36482,7 @@
         <v>2862000</v>
       </c>
     </row>
-    <row r="85" spans="1:17">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>80</v>
       </c>
@@ -36520,7 +36526,7 @@
         <v>25475674</v>
       </c>
     </row>
-    <row r="86" spans="1:17">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>81</v>
       </c>
@@ -36564,7 +36570,7 @@
         <v>1844752.5</v>
       </c>
     </row>
-    <row r="87" spans="1:17">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>82</v>
       </c>
@@ -36608,7 +36614,7 @@
         <v>2747250</v>
       </c>
     </row>
-    <row r="88" spans="1:17">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>83</v>
       </c>
@@ -36652,7 +36658,7 @@
         <v>2014103.5</v>
       </c>
     </row>
-    <row r="89" spans="1:17">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>84</v>
       </c>
@@ -36696,7 +36702,7 @@
         <v>1800357</v>
       </c>
     </row>
-    <row r="90" spans="1:17">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>85</v>
       </c>
@@ -36740,7 +36746,7 @@
         <v>6098800.5</v>
       </c>
     </row>
-    <row r="91" spans="1:17">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>86</v>
       </c>
@@ -36784,7 +36790,7 @@
         <v>1463666.5</v>
       </c>
     </row>
-    <row r="92" spans="1:17">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>87</v>
       </c>
@@ -36828,7 +36834,7 @@
         <v>1247487.5</v>
       </c>
     </row>
-    <row r="93" spans="1:17">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>88</v>
       </c>
@@ -36872,7 +36878,7 @@
         <v>1031467.5</v>
       </c>
     </row>
-    <row r="94" spans="1:17">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>89</v>
       </c>
@@ -36916,7 +36922,7 @@
         <v>660957.5</v>
       </c>
     </row>
-    <row r="95" spans="1:17">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>90</v>
       </c>
@@ -36960,7 +36966,7 @@
         <v>5167640.5</v>
       </c>
     </row>
-    <row r="96" spans="1:17">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>91</v>
       </c>
@@ -37004,7 +37010,7 @@
         <v>282643.5</v>
       </c>
     </row>
-    <row r="97" spans="1:17">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>92</v>
       </c>
@@ -37048,7 +37054,7 @@
         <v>364265</v>
       </c>
     </row>
-    <row r="98" spans="1:17">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>93</v>
       </c>
@@ -37092,7 +37098,7 @@
         <v>298919.5</v>
       </c>
     </row>
-    <row r="99" spans="1:17">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>94</v>
       </c>
@@ -37136,7 +37142,7 @@
         <v>239368.5</v>
       </c>
     </row>
-    <row r="100" spans="1:17">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>95</v>
       </c>
@@ -37180,7 +37186,7 @@
         <v>1049449.5</v>
       </c>
     </row>
-    <row r="101" spans="1:17">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>96</v>
       </c>
@@ -37224,7 +37230,7 @@
         <v>384166.5</v>
       </c>
     </row>
-    <row r="102" spans="1:17">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="10">
         <v>97</v>
       </c>
@@ -37268,7 +37274,7 @@
         <v>288405</v>
       </c>
     </row>
-    <row r="103" spans="1:17">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>98</v>
       </c>
@@ -37312,7 +37318,7 @@
         <v>297470</v>
       </c>
     </row>
-    <row r="104" spans="1:17">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>99</v>
       </c>
@@ -37356,7 +37362,7 @@
         <v>149648</v>
       </c>
     </row>
-    <row r="105" spans="1:17">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>100</v>
       </c>
@@ -37400,7 +37406,7 @@
         <v>606517.5</v>
       </c>
     </row>
-    <row r="106" spans="1:17">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>101</v>
       </c>
@@ -37444,7 +37450,7 @@
         <v>57347.5</v>
       </c>
     </row>
-    <row r="107" spans="1:17">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>102</v>
       </c>
@@ -37488,7 +37494,7 @@
         <v>78105</v>
       </c>
     </row>
-    <row r="108" spans="1:17">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>103</v>
       </c>
@@ -37532,7 +37538,7 @@
         <v>52474.5</v>
       </c>
     </row>
-    <row r="109" spans="1:17">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="10">
         <v>104</v>
       </c>
@@ -37576,7 +37582,7 @@
         <v>32813</v>
       </c>
     </row>
-    <row r="110" spans="1:17">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>105</v>
       </c>
@@ -37620,7 +37626,7 @@
         <v>74166.5</v>
       </c>
     </row>
-    <row r="111" spans="1:17">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>106</v>
       </c>
@@ -37664,7 +37670,7 @@
         <v>23962.5</v>
       </c>
     </row>
-    <row r="112" spans="1:17">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="10">
         <v>107</v>
       </c>
@@ -37708,7 +37714,7 @@
         <v>18490</v>
       </c>
     </row>
-    <row r="113" spans="1:17">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>108</v>
       </c>
@@ -37752,7 +37758,7 @@
         <v>12803</v>
       </c>
     </row>
-    <row r="114" spans="1:17">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="10">
         <v>109</v>
       </c>
@@ -37796,7 +37802,7 @@
         <v>15001.5</v>
       </c>
     </row>
-    <row r="116" spans="1:17">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>116</v>
       </c>
@@ -37859,26 +37865,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD20E48D-FCF7-4BC3-892B-762E6C61C4F1}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:BB119"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.83984375" customWidth="1"/>
-    <col min="4" max="4" width="13.15625" customWidth="1"/>
-    <col min="18" max="18" width="16.15625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.83984375" customWidth="1"/>
-    <col min="22" max="22" width="10.41796875" customWidth="1"/>
-    <col min="24" max="24" width="10.83984375" customWidth="1"/>
-    <col min="25" max="25" width="10.41796875" customWidth="1"/>
-    <col min="27" max="28" width="9.15625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.15625" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="9.15625" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="9.15625" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="9.15625" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="9.15625" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="9.15625" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" customWidth="1"/>
+    <col min="22" max="22" width="10.42578125" customWidth="1"/>
+    <col min="24" max="24" width="10.85546875" customWidth="1"/>
+    <col min="25" max="25" width="10.42578125" customWidth="1"/>
+    <col min="27" max="28" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B1" s="6"/>
       <c r="C1" s="32" t="s">
         <v>134</v>
@@ -37938,7 +37944,7 @@
       <c r="BA1" s="32"/>
       <c r="BB1" s="32"/>
     </row>
-    <row r="2" spans="1:54">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="C2" s="32" t="s">
         <v>129</v>
       </c>
@@ -38009,7 +38015,7 @@
       </c>
       <c r="BB2" s="32"/>
     </row>
-    <row r="3" spans="1:54">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="O3" s="6" t="s">
         <v>161</v>
       </c>
@@ -38017,7 +38023,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:54">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
@@ -38136,7 +38142,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="5" spans="1:54">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>0</v>
       </c>
@@ -38280,7 +38286,7 @@
         <v>1.0992086535555097</v>
       </c>
     </row>
-    <row r="6" spans="1:54">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>1</v>
       </c>
@@ -38424,7 +38430,7 @@
         <v>1.0815418309455558</v>
       </c>
     </row>
-    <row r="7" spans="1:54">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>2</v>
       </c>
@@ -38570,7 +38576,7 @@
         <v>0.81209939049189861</v>
       </c>
     </row>
-    <row r="8" spans="1:54">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>3</v>
       </c>
@@ -38716,7 +38722,7 @@
         <v>0.50939213218573831</v>
       </c>
     </row>
-    <row r="9" spans="1:54">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>4</v>
       </c>
@@ -38862,7 +38868,7 @@
         <v>0.32773879888163232</v>
       </c>
     </row>
-    <row r="10" spans="1:54">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>5</v>
       </c>
@@ -39008,7 +39014,7 @@
         <v>0.17375823526841613</v>
       </c>
     </row>
-    <row r="11" spans="1:54">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>6</v>
       </c>
@@ -39154,7 +39160,7 @@
         <v>6.3031573144374325E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:54">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>7</v>
       </c>
@@ -39300,7 +39306,7 @@
         <v>2.0988230534600479E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:54">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>8</v>
       </c>
@@ -39446,7 +39452,7 @@
         <v>7.025979663887327E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:54">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>9</v>
       </c>
@@ -39592,7 +39598,7 @@
         <v>2.5682638758206021E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:54">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>10</v>
       </c>
@@ -39738,7 +39744,7 @@
         <v>1.5659405702452441E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:54">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>11</v>
       </c>
@@ -39856,7 +39862,7 @@
       <c r="AR16" s="26"/>
       <c r="AS16" s="26"/>
     </row>
-    <row r="17" spans="1:34">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>12</v>
       </c>
@@ -39895,7 +39901,7 @@
       <c r="AG17" s="24"/>
       <c r="AH17" s="24"/>
     </row>
-    <row r="18" spans="1:34">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>13</v>
       </c>
@@ -39973,7 +39979,7 @@
         <v>0.50373475402895607</v>
       </c>
     </row>
-    <row r="19" spans="1:34">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>14</v>
       </c>
@@ -40016,7 +40022,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="20" spans="1:34">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>15</v>
       </c>
@@ -40047,7 +40053,7 @@
       <c r="X20" s="22"/>
       <c r="Y20" s="22"/>
     </row>
-    <row r="21" spans="1:34">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>16</v>
       </c>
@@ -40078,7 +40084,7 @@
       <c r="X21" s="21"/>
       <c r="Y21" s="21"/>
     </row>
-    <row r="22" spans="1:34">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>17</v>
       </c>
@@ -40109,7 +40115,7 @@
       <c r="X22" s="21"/>
       <c r="Y22" s="21"/>
     </row>
-    <row r="23" spans="1:34">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>18</v>
       </c>
@@ -40140,7 +40146,7 @@
       <c r="X23" s="21"/>
       <c r="Y23" s="21"/>
     </row>
-    <row r="24" spans="1:34">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>19</v>
       </c>
@@ -40171,7 +40177,7 @@
       <c r="X24" s="21"/>
       <c r="Y24" s="21"/>
     </row>
-    <row r="25" spans="1:34">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>20</v>
       </c>
@@ -40202,7 +40208,7 @@
       <c r="X25" s="21"/>
       <c r="Y25" s="21"/>
     </row>
-    <row r="26" spans="1:34">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>21</v>
       </c>
@@ -40233,7 +40239,7 @@
       <c r="X26" s="21"/>
       <c r="Y26" s="21"/>
     </row>
-    <row r="27" spans="1:34">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>22</v>
       </c>
@@ -40264,7 +40270,7 @@
       <c r="X27" s="21"/>
       <c r="Y27" s="21"/>
     </row>
-    <row r="28" spans="1:34">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>23</v>
       </c>
@@ -40295,7 +40301,7 @@
       <c r="X28" s="21"/>
       <c r="Y28" s="21"/>
     </row>
-    <row r="29" spans="1:34">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>24</v>
       </c>
@@ -40326,7 +40332,7 @@
       <c r="X29" s="21"/>
       <c r="Y29" s="21"/>
     </row>
-    <row r="30" spans="1:34">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>25</v>
       </c>
@@ -40357,7 +40363,7 @@
       <c r="X30" s="21"/>
       <c r="Y30" s="21"/>
     </row>
-    <row r="31" spans="1:34">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>26</v>
       </c>
@@ -40388,7 +40394,7 @@
       <c r="X31" s="21"/>
       <c r="Y31" s="21"/>
     </row>
-    <row r="32" spans="1:34">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>27</v>
       </c>
@@ -40419,7 +40425,7 @@
       <c r="X32" s="21"/>
       <c r="Y32" s="21"/>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>28</v>
       </c>
@@ -40450,7 +40456,7 @@
       <c r="X33" s="21"/>
       <c r="Y33" s="21"/>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>29</v>
       </c>
@@ -40481,7 +40487,7 @@
       <c r="X34" s="21"/>
       <c r="Y34" s="21"/>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>30</v>
       </c>
@@ -40512,7 +40518,7 @@
       <c r="X35" s="21"/>
       <c r="Y35" s="21"/>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>31</v>
       </c>
@@ -40543,7 +40549,7 @@
       <c r="X36" s="21"/>
       <c r="Y36" s="21"/>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>32</v>
       </c>
@@ -40574,7 +40580,7 @@
       <c r="X37" s="21"/>
       <c r="Y37" s="21"/>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>33</v>
       </c>
@@ -40605,7 +40611,7 @@
       <c r="X38" s="21"/>
       <c r="Y38" s="21"/>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>34</v>
       </c>
@@ -40636,7 +40642,7 @@
       <c r="X39" s="21"/>
       <c r="Y39" s="21"/>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>35</v>
       </c>
@@ -40667,7 +40673,7 @@
       <c r="X40" s="21"/>
       <c r="Y40" s="21"/>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>36</v>
       </c>
@@ -40698,7 +40704,7 @@
       <c r="X41" s="21"/>
       <c r="Y41" s="21"/>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>37</v>
       </c>
@@ -40729,7 +40735,7 @@
       <c r="X42" s="21"/>
       <c r="Y42" s="21"/>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>38</v>
       </c>
@@ -40760,7 +40766,7 @@
       <c r="X43" s="21"/>
       <c r="Y43" s="21"/>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>39</v>
       </c>
@@ -40791,7 +40797,7 @@
       <c r="X44" s="21"/>
       <c r="Y44" s="21"/>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>40</v>
       </c>
@@ -40822,7 +40828,7 @@
       <c r="X45" s="21"/>
       <c r="Y45" s="21"/>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>41</v>
       </c>
@@ -40853,7 +40859,7 @@
       <c r="X46" s="21"/>
       <c r="Y46" s="21"/>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <v>42</v>
       </c>
@@ -40884,7 +40890,7 @@
       <c r="X47" s="21"/>
       <c r="Y47" s="21"/>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <v>43</v>
       </c>
@@ -40915,7 +40921,7 @@
       <c r="X48" s="21"/>
       <c r="Y48" s="21"/>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="10">
         <v>44</v>
       </c>
@@ -40946,7 +40952,7 @@
       <c r="X49" s="21"/>
       <c r="Y49" s="21"/>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>45</v>
       </c>
@@ -40977,7 +40983,7 @@
       <c r="X50" s="21"/>
       <c r="Y50" s="21"/>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>46</v>
       </c>
@@ -41008,7 +41014,7 @@
       <c r="X51" s="21"/>
       <c r="Y51" s="21"/>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>47</v>
       </c>
@@ -41039,7 +41045,7 @@
       <c r="X52" s="21"/>
       <c r="Y52" s="21"/>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>48</v>
       </c>
@@ -41070,7 +41076,7 @@
       <c r="X53" s="21"/>
       <c r="Y53" s="21"/>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>49</v>
       </c>
@@ -41101,7 +41107,7 @@
       <c r="X54" s="21"/>
       <c r="Y54" s="21"/>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>50</v>
       </c>
@@ -41132,7 +41138,7 @@
       <c r="X55" s="21"/>
       <c r="Y55" s="21"/>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>51</v>
       </c>
@@ -41163,7 +41169,7 @@
       <c r="X56" s="21"/>
       <c r="Y56" s="21"/>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>52</v>
       </c>
@@ -41194,7 +41200,7 @@
       <c r="X57" s="21"/>
       <c r="Y57" s="21"/>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>53</v>
       </c>
@@ -41225,7 +41231,7 @@
       <c r="X58" s="21"/>
       <c r="Y58" s="21"/>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>54</v>
       </c>
@@ -41256,7 +41262,7 @@
       <c r="X59" s="21"/>
       <c r="Y59" s="21"/>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="10">
         <v>55</v>
       </c>
@@ -41287,7 +41293,7 @@
       <c r="X60" s="21"/>
       <c r="Y60" s="21"/>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>56</v>
       </c>
@@ -41318,7 +41324,7 @@
       <c r="X61" s="21"/>
       <c r="Y61" s="21"/>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>57</v>
       </c>
@@ -41349,7 +41355,7 @@
       <c r="X62" s="21"/>
       <c r="Y62" s="21"/>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>58</v>
       </c>
@@ -41380,7 +41386,7 @@
       <c r="X63" s="21"/>
       <c r="Y63" s="21"/>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>59</v>
       </c>
@@ -41411,7 +41417,7 @@
       <c r="X64" s="21"/>
       <c r="Y64" s="21"/>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>60</v>
       </c>
@@ -41442,7 +41448,7 @@
       <c r="X65" s="21"/>
       <c r="Y65" s="21"/>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>61</v>
       </c>
@@ -41473,7 +41479,7 @@
       <c r="X66" s="21"/>
       <c r="Y66" s="21"/>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>62</v>
       </c>
@@ -41504,7 +41510,7 @@
       <c r="X67" s="21"/>
       <c r="Y67" s="21"/>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>63</v>
       </c>
@@ -41535,7 +41541,7 @@
       <c r="X68" s="21"/>
       <c r="Y68" s="21"/>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>64</v>
       </c>
@@ -41566,7 +41572,7 @@
       <c r="X69" s="21"/>
       <c r="Y69" s="21"/>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>65</v>
       </c>
@@ -41597,7 +41603,7 @@
       <c r="X70" s="21"/>
       <c r="Y70" s="21"/>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>66</v>
       </c>
@@ -41628,7 +41634,7 @@
       <c r="X71" s="21"/>
       <c r="Y71" s="21"/>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>67</v>
       </c>
@@ -41659,7 +41665,7 @@
       <c r="X72" s="21"/>
       <c r="Y72" s="21"/>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>68</v>
       </c>
@@ -41690,7 +41696,7 @@
       <c r="X73" s="21"/>
       <c r="Y73" s="21"/>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>69</v>
       </c>
@@ -41721,7 +41727,7 @@
       <c r="X74" s="21"/>
       <c r="Y74" s="21"/>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>70</v>
       </c>
@@ -41752,7 +41758,7 @@
       <c r="X75" s="21"/>
       <c r="Y75" s="21"/>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>71</v>
       </c>
@@ -41783,7 +41789,7 @@
       <c r="X76" s="21"/>
       <c r="Y76" s="21"/>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>72</v>
       </c>
@@ -41814,7 +41820,7 @@
       <c r="X77" s="21"/>
       <c r="Y77" s="21"/>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>73</v>
       </c>
@@ -41845,7 +41851,7 @@
       <c r="X78" s="21"/>
       <c r="Y78" s="21"/>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>74</v>
       </c>
@@ -41876,7 +41882,7 @@
       <c r="X79" s="21"/>
       <c r="Y79" s="21"/>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>75</v>
       </c>
@@ -41907,7 +41913,7 @@
       <c r="X80" s="21"/>
       <c r="Y80" s="21"/>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>76</v>
       </c>
@@ -41938,7 +41944,7 @@
       <c r="X81" s="21"/>
       <c r="Y81" s="21"/>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>77</v>
       </c>
@@ -41969,7 +41975,7 @@
       <c r="X82" s="21"/>
       <c r="Y82" s="21"/>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>78</v>
       </c>
@@ -42000,7 +42006,7 @@
       <c r="X83" s="21"/>
       <c r="Y83" s="21"/>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>79</v>
       </c>
@@ -42031,7 +42037,7 @@
       <c r="X84" s="21"/>
       <c r="Y84" s="21"/>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>80</v>
       </c>
@@ -42062,7 +42068,7 @@
       <c r="X85" s="21"/>
       <c r="Y85" s="21"/>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>81</v>
       </c>
@@ -42093,7 +42099,7 @@
       <c r="X86" s="21"/>
       <c r="Y86" s="21"/>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>82</v>
       </c>
@@ -42124,7 +42130,7 @@
       <c r="X87" s="21"/>
       <c r="Y87" s="21"/>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>83</v>
       </c>
@@ -42155,7 +42161,7 @@
       <c r="X88" s="21"/>
       <c r="Y88" s="21"/>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>84</v>
       </c>
@@ -42186,7 +42192,7 @@
       <c r="X89" s="21"/>
       <c r="Y89" s="21"/>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>85</v>
       </c>
@@ -42217,7 +42223,7 @@
       <c r="X90" s="21"/>
       <c r="Y90" s="21"/>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>86</v>
       </c>
@@ -42248,7 +42254,7 @@
       <c r="X91" s="21"/>
       <c r="Y91" s="21"/>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>87</v>
       </c>
@@ -42279,7 +42285,7 @@
       <c r="X92" s="21"/>
       <c r="Y92" s="21"/>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>88</v>
       </c>
@@ -42310,7 +42316,7 @@
       <c r="X93" s="21"/>
       <c r="Y93" s="21"/>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>89</v>
       </c>
@@ -42341,7 +42347,7 @@
       <c r="X94" s="21"/>
       <c r="Y94" s="21"/>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>90</v>
       </c>
@@ -42372,7 +42378,7 @@
       <c r="X95" s="21"/>
       <c r="Y95" s="21"/>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>91</v>
       </c>
@@ -42403,7 +42409,7 @@
       <c r="X96" s="21"/>
       <c r="Y96" s="21"/>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>92</v>
       </c>
@@ -42434,7 +42440,7 @@
       <c r="X97" s="21"/>
       <c r="Y97" s="21"/>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>93</v>
       </c>
@@ -42465,7 +42471,7 @@
       <c r="X98" s="21"/>
       <c r="Y98" s="21"/>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>94</v>
       </c>
@@ -42496,7 +42502,7 @@
       <c r="X99" s="21"/>
       <c r="Y99" s="21"/>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>95</v>
       </c>
@@ -42527,7 +42533,7 @@
       <c r="X100" s="21"/>
       <c r="Y100" s="21"/>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>96</v>
       </c>
@@ -42558,7 +42564,7 @@
       <c r="X101" s="21"/>
       <c r="Y101" s="21"/>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" s="10">
         <v>97</v>
       </c>
@@ -42589,7 +42595,7 @@
       <c r="X102" s="21"/>
       <c r="Y102" s="21"/>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>98</v>
       </c>
@@ -42620,7 +42626,7 @@
       <c r="X103" s="21"/>
       <c r="Y103" s="21"/>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>99</v>
       </c>
@@ -42651,7 +42657,7 @@
       <c r="X104" s="21"/>
       <c r="Y104" s="21"/>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>100</v>
       </c>
@@ -42682,7 +42688,7 @@
       <c r="X105" s="21"/>
       <c r="Y105" s="21"/>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>101</v>
       </c>
@@ -42713,7 +42719,7 @@
       <c r="X106" s="21"/>
       <c r="Y106" s="21"/>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>102</v>
       </c>
@@ -42744,7 +42750,7 @@
       <c r="X107" s="21"/>
       <c r="Y107" s="21"/>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>103</v>
       </c>
@@ -42775,7 +42781,7 @@
       <c r="X108" s="21"/>
       <c r="Y108" s="21"/>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" s="10">
         <v>104</v>
       </c>
@@ -42806,7 +42812,7 @@
       <c r="X109" s="21"/>
       <c r="Y109" s="21"/>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>105</v>
       </c>
@@ -42837,7 +42843,7 @@
       <c r="X110" s="21"/>
       <c r="Y110" s="21"/>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>106</v>
       </c>
@@ -42868,7 +42874,7 @@
       <c r="X111" s="21"/>
       <c r="Y111" s="21"/>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" s="10">
         <v>107</v>
       </c>
@@ -42899,7 +42905,7 @@
       <c r="X112" s="21"/>
       <c r="Y112" s="21"/>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>108</v>
       </c>
@@ -42930,7 +42936,7 @@
       <c r="X113" s="21"/>
       <c r="Y113" s="21"/>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" s="10">
         <v>109</v>
       </c>
@@ -42961,14 +42967,14 @@
       <c r="X114" s="21"/>
       <c r="Y114" s="21"/>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" s="10"/>
       <c r="F115" s="4"/>
       <c r="G115" s="4"/>
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>116</v>
       </c>
@@ -43005,11 +43011,11 @@
       <c r="X116" s="18"/>
       <c r="Y116" s="18"/>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="F119" s="4"/>

--- a/workbooks/ru-vs-mx-1897.xlsx
+++ b/workbooks/ru-vs-mx-1897.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50871EE-937C-4289-B8D8-7B59455E9A96}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2476FA60-DDBB-4F35-9C4A-5BBF0A685EE4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="9" xr2:uid="{ADE3E715-68A0-475F-BFDD-EA0E2833FCCA}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="10" xr2:uid="{ADE3E715-68A0-475F-BFDD-EA0E2833FCCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -23,8 +23,10 @@
     <sheet name="RU-1897" sheetId="7" r:id="rId8"/>
     <sheet name="RU-vs-MX" sheetId="10" r:id="rId9"/>
     <sheet name="RU-vs-MX v2" sheetId="15" r:id="rId10"/>
+    <sheet name="MX-Teran" sheetId="16" r:id="rId11"/>
+    <sheet name="MX-Teran-vs-RU" sheetId="17" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,12 +34,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -45,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="196">
   <si>
     <t>M</t>
   </si>
@@ -572,6 +569,69 @@
   <si>
     <t>MX1900</t>
   </si>
+  <si>
+    <t>0-9</t>
+  </si>
+  <si>
+    <t>70-79</t>
+  </si>
+  <si>
+    <t>80 +</t>
+  </si>
+  <si>
+    <t>MX 1910</t>
+  </si>
+  <si>
+    <t>verfy</t>
+  </si>
+  <si>
+    <t>в процентах:</t>
+  </si>
+  <si>
+    <t>RU-1897, агрегарция по возрастным группам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verify </t>
+  </si>
+  <si>
+    <t>в процентах</t>
+  </si>
+  <si>
+    <t>MX1910</t>
+  </si>
+  <si>
+    <t>мужчины</t>
+  </si>
+  <si>
+    <t>женщины</t>
+  </si>
+  <si>
+    <t>MX-Teran</t>
+  </si>
+  <si>
+    <t>Структура населения Мексики по переписям 1895, 1900 и 1910 годов</t>
+  </si>
+  <si>
+    <t>M. Mier-y-Teran, "Evolution de la population mexicaine a partir des donnees des recensements : 1895-1970", 1982, диссертация Université de Montréal, т. 2 (Annexes), стр. 526-527 (таблица XVII.4)</t>
+  </si>
+  <si>
+    <t>Там же - агрегация русской переписи 1897 года по тем же возрастным группам.</t>
+  </si>
+  <si>
+    <t>с коррекцией Мийе-и-Теран и разбивкой по 10-летним возрастным группам</t>
+  </si>
+  <si>
+    <t>MX-Teran-vs-RU</t>
+  </si>
+  <si>
+    <t>Графики для данных со страницы MX-Teran</t>
+  </si>
+  <si>
+    <t>в процентах на группу</t>
+  </si>
+  <si>
+    <t>в процентах на год возраста</t>
+  </si>
 </sst>
 </file>
 
@@ -646,7 +706,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -704,6 +764,9 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -714,6 +777,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3688,6 +3766,1535 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="647992880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1600" b="1" i="0" baseline="0"/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1920" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Мужчины</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1920" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.8154183211196739E-2"/>
+          <c:y val="0.10007910717126822"/>
+          <c:w val="0.9418111743415174"/>
+          <c:h val="0.77919385797855745"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MX-Teran-vs-RU'!$B$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MX1895</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$A$30:$A$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$B$30:$B$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.4785951717743315</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.057322248715723</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.81745553532203297</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61251154249787765</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.44061784711287155</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.3050895850621218</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.18476749963633771</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.424886150625897E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.1937990566106801E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-72B1-4821-A8BC-0E5511636CBE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MX-Teran-vs-RU'!$C$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MX1900</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$A$30:$A$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$C$30:$C$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.4853729654266892</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0431289996112918</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8090816259300786</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.59921369133224778</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.44920887099862783</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.30710807716231581</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.18299072280205625</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.3068774054895452E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.3128622495389134E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-72B1-4821-A8BC-0E5511636CBE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MX-Teran-vs-RU'!$D$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MX1910</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="7030A0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$A$30:$A$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$D$30:$D$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.511217722683833</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0506361829235888</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.81018632241051147</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.59719671169022437</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.43206014868392073</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.29324609655844214</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.17432365614743511</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9212560531936196E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2987920289866556E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-72B1-4821-A8BC-0E5511636CBE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MX-Teran-vs-RU'!$E$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RU1897</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$A$30:$A$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$E$30:$E$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.3528830731458645</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0428829401381108</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.77093078936995973</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61181217155265455</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.46672279614042755</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.32634264142568747</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.21408399642337211</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.387090287589285E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.098001675978369E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-72B1-4821-A8BC-0E5511636CBE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="886677488"/>
+        <c:axId val="886678144"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="886677488"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="90"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="886678144"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="886678144"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="886677488"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1600" b="1" i="0" baseline="0"/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1920" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Женщины</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1920" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MX-Teran-vs-RU'!$I$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MX1895</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$H$30:$H$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$I$30:$I$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.4450658268534602</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0442614408793338</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8317561371393577</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.62499860742011126</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.45892271293023956</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.33448416135337755</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.2013734179894584</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.2271713185201023E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.4318904295862269E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-61A3-4366-95B0-939197FD478A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MX-Teran-vs-RU'!$J$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MX1900</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$H$30:$H$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$J$30:$J$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.450429581969223</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0455611770770465</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8131447929905159</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.62031677442350053</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.46555838612589129</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.33620616412817772</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.20716355868869901</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.2971368098723949E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6345846684630298E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-61A3-4366-95B0-939197FD478A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MX-Teran-vs-RU'!$K$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MX1910</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="7030A0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$H$30:$H$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$K$30:$K$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.4777359748421692</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0553106192310762</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.81190514677954506</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61925682867857468</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.45112833589275059</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.32576641209841051</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.20603969658886986</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.4909131441002123E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6880532527843238E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-61A3-4366-95B0-939197FD478A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MX-Teran-vs-RU'!$L$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RU1897</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$H$30:$H$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'MX-Teran-vs-RU'!$L$30:$L$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.3699237966410873</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0866303903396397</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.81363616062742383</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6300776957885984</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.47771272565851974</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.34648610606953911</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22835706957034593</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.10298551382201149</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.3681213651080892E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-61A3-4366-95B0-939197FD478A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="886968656"/>
+        <c:axId val="886935376"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="886968656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="90"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="886935376"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="886935376"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="886968656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -11344,6 +12951,86 @@
 </file>
 
 <file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -12736,6 +14423,1038 @@
 </file>
 
 <file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -17808,6 +20527,83 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13913827-B3CF-4257-A257-1C8C0281600B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75B5D18F-5ED4-4B08-8453-B25219358A7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -18106,7 +20902,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FE6297-7AA9-4082-887A-7490FB1B1C69}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" customWidth="1"/>
@@ -18322,6 +21118,37 @@
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B48" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B53" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -18349,16 +21176,16 @@
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B1" s="6"/>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
       <c r="M1" s="15"/>
       <c r="N1" s="15"/>
       <c r="O1" s="15"/>
@@ -18374,109 +21201,109 @@
       <c r="W1" s="25"/>
       <c r="X1" s="25"/>
       <c r="Y1" s="25"/>
-      <c r="AA1" s="32" t="s">
+      <c r="AA1" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AJ1" s="32" t="s">
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33"/>
+      <c r="AJ1" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="32"/>
+      <c r="AK1" s="33"/>
+      <c r="AL1" s="33"/>
+      <c r="AM1" s="33"/>
+      <c r="AN1" s="33"/>
+      <c r="AO1" s="33"/>
+      <c r="AP1" s="33"/>
+      <c r="AQ1" s="33"/>
       <c r="AR1" s="6"/>
       <c r="AS1" s="6"/>
-      <c r="AU1" s="32" t="s">
+      <c r="AU1" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="AV1" s="32"/>
-      <c r="AW1" s="32"/>
-      <c r="AX1" s="32"/>
-      <c r="AY1" s="32"/>
-      <c r="AZ1" s="32"/>
-      <c r="BA1" s="32"/>
-      <c r="BB1" s="32"/>
+      <c r="AV1" s="33"/>
+      <c r="AW1" s="33"/>
+      <c r="AX1" s="33"/>
+      <c r="AY1" s="33"/>
+      <c r="AZ1" s="33"/>
+      <c r="BA1" s="33"/>
+      <c r="BB1" s="33"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="F2" s="32" t="s">
+      <c r="D2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="I2" s="32" t="s">
+      <c r="G2" s="33"/>
+      <c r="I2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="M2" s="32" t="s">
+      <c r="J2" s="33"/>
+      <c r="M2" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="N2" s="32"/>
+      <c r="N2" s="33"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="32" t="s">
+      <c r="R2" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="S2" s="32"/>
-      <c r="U2" s="32" t="s">
+      <c r="S2" s="33"/>
+      <c r="U2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="V2" s="32"/>
-      <c r="X2" s="32" t="s">
+      <c r="V2" s="33"/>
+      <c r="X2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="Y2" s="32"/>
-      <c r="AA2" s="32" t="s">
+      <c r="Y2" s="33"/>
+      <c r="AA2" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="AB2" s="32"/>
-      <c r="AD2" s="32" t="s">
+      <c r="AB2" s="33"/>
+      <c r="AD2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="AE2" s="32"/>
-      <c r="AG2" s="32" t="s">
+      <c r="AE2" s="33"/>
+      <c r="AG2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="AH2" s="32"/>
-      <c r="AJ2" s="32" t="s">
+      <c r="AH2" s="33"/>
+      <c r="AJ2" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="AK2" s="32"/>
-      <c r="AM2" s="32" t="s">
+      <c r="AK2" s="33"/>
+      <c r="AM2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="AN2" s="32"/>
-      <c r="AP2" s="32" t="s">
+      <c r="AN2" s="33"/>
+      <c r="AP2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="AQ2" s="32"/>
+      <c r="AQ2" s="33"/>
       <c r="AR2" s="6"/>
       <c r="AS2" s="6"/>
-      <c r="AU2" s="32" t="s">
+      <c r="AU2" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="AV2" s="32"/>
-      <c r="AX2" s="32" t="s">
+      <c r="AV2" s="33"/>
+      <c r="AX2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="AY2" s="32"/>
-      <c r="BA2" s="32" t="s">
+      <c r="AY2" s="33"/>
+      <c r="BA2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="BB2" s="32"/>
+      <c r="BB2" s="33"/>
     </row>
     <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="O3" s="6" t="s">
@@ -23524,6 +26351,10 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AM2:AN2"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="AA1:AH1"/>
+    <mergeCell ref="AJ1:AQ1"/>
     <mergeCell ref="AU1:BB1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="F2:G2"/>
@@ -23540,15 +26371,3652 @@
     <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="AG2:AH2"/>
     <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="AA1:AH1"/>
-    <mergeCell ref="AJ1:AQ1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="R5:Y16" formulaRange="1"/>
+    <ignoredError sqref="R6:Y16 R5:T5 V5:Y5" formulaRange="1"/>
   </ignoredErrors>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6479BE9-21F4-4C28-8A18-AF6C27ADB2DD}">
+  <dimension ref="A3:T148"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="42"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="H3" s="42"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="K3" s="42"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="34"/>
+      <c r="J4" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="9">
+        <v>1858092</v>
+      </c>
+      <c r="E5" s="37">
+        <v>1815957</v>
+      </c>
+      <c r="F5" s="37"/>
+      <c r="G5" s="9">
+        <v>2024528</v>
+      </c>
+      <c r="H5" s="37">
+        <v>1976901</v>
+      </c>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37">
+        <v>2288599</v>
+      </c>
+      <c r="K5" s="37">
+        <v>2237894</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="9">
+        <v>1328695</v>
+      </c>
+      <c r="E6" s="37">
+        <v>1312282</v>
+      </c>
+      <c r="F6" s="37"/>
+      <c r="G6" s="9">
+        <v>1421760</v>
+      </c>
+      <c r="H6" s="37">
+        <v>1425075</v>
+      </c>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37">
+        <v>1591091</v>
+      </c>
+      <c r="K6" s="37">
+        <v>1598170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="9">
+        <v>1027264</v>
+      </c>
+      <c r="E7" s="37">
+        <v>1045235</v>
+      </c>
+      <c r="F7" s="37"/>
+      <c r="G7" s="9">
+        <v>1102759</v>
+      </c>
+      <c r="H7" s="37">
+        <v>1108297</v>
+      </c>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37">
+        <v>1226952</v>
+      </c>
+      <c r="K7" s="37">
+        <v>1229555</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="9">
+        <v>769719</v>
+      </c>
+      <c r="E8" s="37">
+        <v>785411</v>
+      </c>
+      <c r="F8" s="37"/>
+      <c r="G8" s="9">
+        <v>816714</v>
+      </c>
+      <c r="H8" s="37">
+        <v>845477</v>
+      </c>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37">
+        <v>904399</v>
+      </c>
+      <c r="K8" s="37">
+        <v>937807</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="9">
+        <v>553707</v>
+      </c>
+      <c r="E9" s="37">
+        <v>576710</v>
+      </c>
+      <c r="F9" s="37"/>
+      <c r="G9" s="9">
+        <v>612261</v>
+      </c>
+      <c r="H9" s="37">
+        <v>634545</v>
+      </c>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37">
+        <v>654315</v>
+      </c>
+      <c r="K9" s="37">
+        <v>683192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="9">
+        <v>383394</v>
+      </c>
+      <c r="E10" s="37">
+        <v>420333</v>
+      </c>
+      <c r="F10" s="37"/>
+      <c r="G10" s="9">
+        <v>418581</v>
+      </c>
+      <c r="H10" s="37">
+        <v>458241</v>
+      </c>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37">
+        <v>444094</v>
+      </c>
+      <c r="K10" s="37">
+        <v>493343</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="9">
+        <v>232190</v>
+      </c>
+      <c r="E11" s="37">
+        <v>253058</v>
+      </c>
+      <c r="F11" s="37"/>
+      <c r="G11" s="9">
+        <v>249412</v>
+      </c>
+      <c r="H11" s="37">
+        <v>282359</v>
+      </c>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37">
+        <v>263997</v>
+      </c>
+      <c r="K11" s="37">
+        <v>312028</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="9">
+        <v>80739</v>
+      </c>
+      <c r="E12" s="37">
+        <v>90821</v>
+      </c>
+      <c r="F12" s="37"/>
+      <c r="G12" s="9">
+        <v>99591</v>
+      </c>
+      <c r="H12" s="37">
+        <v>113088</v>
+      </c>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37">
+        <v>104816</v>
+      </c>
+      <c r="K12" s="37">
+        <v>128587</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="9">
+        <v>15002</v>
+      </c>
+      <c r="E13" s="37">
+        <v>17994</v>
+      </c>
+      <c r="F13" s="37"/>
+      <c r="G13" s="9">
+        <v>17894</v>
+      </c>
+      <c r="H13" s="37">
+        <v>22279</v>
+      </c>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37">
+        <v>19669</v>
+      </c>
+      <c r="K13" s="37">
+        <v>25564</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="9">
+        <v>6248802</v>
+      </c>
+      <c r="E14" s="37">
+        <v>6317802</v>
+      </c>
+      <c r="F14" s="37"/>
+      <c r="G14" s="9">
+        <v>6763500</v>
+      </c>
+      <c r="H14" s="37">
+        <v>6866262</v>
+      </c>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37">
+        <v>7497932</v>
+      </c>
+      <c r="K14" s="37">
+        <v>7646140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="4">
+        <f>SUM(D5:D13)-D14</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <f>SUM(E5:E13)-E14</f>
+        <v>-1</v>
+      </c>
+      <c r="G15" s="4">
+        <f>SUM(G5:G13)-G14</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>SUM(H5:H13)-H14</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <f>SUM(J5:J13)-J14</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <f>SUM(K5:K13)-K14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="4">
+        <f>D14+E14</f>
+        <v>12566604</v>
+      </c>
+      <c r="E16" s="4">
+        <f>D16</f>
+        <v>12566604</v>
+      </c>
+      <c r="G16" s="4">
+        <f>G14+H14</f>
+        <v>13629762</v>
+      </c>
+      <c r="H16" s="4">
+        <f>G16</f>
+        <v>13629762</v>
+      </c>
+      <c r="J16" s="4">
+        <f>J14+K14</f>
+        <v>15144072</v>
+      </c>
+      <c r="K16" s="4">
+        <f>J16</f>
+        <v>15144072</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="N18" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="40"/>
+      <c r="S18" s="40"/>
+      <c r="T18" s="40"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="N19" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>133</v>
+      </c>
+      <c r="T19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="39"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="D21" s="38">
+        <f>100*D5/D$16</f>
+        <v>14.785951717743314</v>
+      </c>
+      <c r="E21" s="38">
+        <f>100*E5/E$16</f>
+        <v>14.450658268534601</v>
+      </c>
+      <c r="G21" s="38">
+        <f>100*G5/G$16</f>
+        <v>14.853729654266891</v>
+      </c>
+      <c r="H21" s="38">
+        <f>100*H5/H$16</f>
+        <v>14.50429581969223</v>
+      </c>
+      <c r="J21" s="38">
+        <f>100*J5/J$16</f>
+        <v>15.11217722683833</v>
+      </c>
+      <c r="K21" s="38">
+        <f>100*K5/K$16</f>
+        <v>14.777359748421693</v>
+      </c>
+      <c r="N21" s="38">
+        <f>(D21+E21) * $B21</f>
+        <v>146.18304993138958</v>
+      </c>
+      <c r="Q21" s="38">
+        <f>(G21+H21) * $B21</f>
+        <v>146.79012736979561</v>
+      </c>
+      <c r="T21" s="38">
+        <f>(J21+K21) * $B21</f>
+        <v>149.44768487630012</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22">
+        <f>B21+10</f>
+        <v>15</v>
+      </c>
+      <c r="D22" s="38">
+        <f t="shared" ref="D22:E22" si="0">100*D6/D$16</f>
+        <v>10.57322248715723</v>
+      </c>
+      <c r="E22" s="38">
+        <f t="shared" si="0"/>
+        <v>10.442614408793338</v>
+      </c>
+      <c r="G22" s="38">
+        <f t="shared" ref="G22:H22" si="1">100*G6/G$16</f>
+        <v>10.431289996112918</v>
+      </c>
+      <c r="H22" s="38">
+        <f t="shared" si="1"/>
+        <v>10.455611770770465</v>
+      </c>
+      <c r="J22" s="38">
+        <f t="shared" ref="J22:K22" si="2">100*J6/J$16</f>
+        <v>10.506361829235889</v>
+      </c>
+      <c r="K22" s="38">
+        <f t="shared" si="2"/>
+        <v>10.553106192310761</v>
+      </c>
+      <c r="N22" s="38">
+        <f t="shared" ref="N22:N29" si="3">(D22+E22) * $B22</f>
+        <v>315.23755343925853</v>
+      </c>
+      <c r="Q22" s="38">
+        <f t="shared" ref="Q22:Q29" si="4">(G22+H22) * $B22</f>
+        <v>313.30352650325074</v>
+      </c>
+      <c r="T22" s="38">
+        <f t="shared" ref="T22:T29" si="5">(J22+K22) * $B22</f>
+        <v>315.89202032319974</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23">
+        <f t="shared" ref="B23:B28" si="6">B22+10</f>
+        <v>25</v>
+      </c>
+      <c r="D23" s="38">
+        <f t="shared" ref="D23:E23" si="7">100*D7/D$16</f>
+        <v>8.1745553532203292</v>
+      </c>
+      <c r="E23" s="38">
+        <f t="shared" si="7"/>
+        <v>8.3175613713935768</v>
+      </c>
+      <c r="G23" s="38">
+        <f t="shared" ref="G23:H23" si="8">100*G7/G$16</f>
+        <v>8.0908162593007855</v>
+      </c>
+      <c r="H23" s="38">
+        <f t="shared" si="8"/>
+        <v>8.1314479299051587</v>
+      </c>
+      <c r="J23" s="38">
+        <f t="shared" ref="J23:K23" si="9">100*J7/J$16</f>
+        <v>8.1018632241051147</v>
+      </c>
+      <c r="K23" s="38">
+        <f t="shared" si="9"/>
+        <v>8.1190514677954511</v>
+      </c>
+      <c r="N23" s="38">
+        <f t="shared" si="3"/>
+        <v>412.30291811534767</v>
+      </c>
+      <c r="Q23" s="38">
+        <f t="shared" si="4"/>
+        <v>405.55660473014859</v>
+      </c>
+      <c r="T23" s="38">
+        <f t="shared" si="5"/>
+        <v>405.52286729751421</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+      <c r="D24" s="38">
+        <f t="shared" ref="D24:E24" si="10">100*D8/D$16</f>
+        <v>6.1251154249787767</v>
+      </c>
+      <c r="E24" s="38">
+        <f t="shared" si="10"/>
+        <v>6.2499860742011126</v>
+      </c>
+      <c r="G24" s="38">
+        <f t="shared" ref="G24:H24" si="11">100*G8/G$16</f>
+        <v>5.9921369133224776</v>
+      </c>
+      <c r="H24" s="38">
+        <f t="shared" si="11"/>
+        <v>6.2031677442350057</v>
+      </c>
+      <c r="J24" s="38">
+        <f t="shared" ref="J24:K24" si="12">100*J8/J$16</f>
+        <v>5.9719671169022437</v>
+      </c>
+      <c r="K24" s="38">
+        <f t="shared" si="12"/>
+        <v>6.1925682867857468</v>
+      </c>
+      <c r="N24" s="38">
+        <f t="shared" si="3"/>
+        <v>433.12855247129613</v>
+      </c>
+      <c r="Q24" s="38">
+        <f t="shared" si="4"/>
+        <v>426.83566301451191</v>
+      </c>
+      <c r="T24" s="38">
+        <f t="shared" si="5"/>
+        <v>425.75873912907969</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="6"/>
+        <v>45</v>
+      </c>
+      <c r="D25" s="38">
+        <f t="shared" ref="D25:E25" si="13">100*D9/D$16</f>
+        <v>4.4061784711287153</v>
+      </c>
+      <c r="E25" s="38">
+        <f t="shared" si="13"/>
+        <v>4.5892271293023956</v>
+      </c>
+      <c r="G25" s="38">
+        <f t="shared" ref="G25:H25" si="14">100*G9/G$16</f>
+        <v>4.4920887099862785</v>
+      </c>
+      <c r="H25" s="38">
+        <f t="shared" si="14"/>
+        <v>4.6555838612589131</v>
+      </c>
+      <c r="J25" s="38">
+        <f t="shared" ref="J25:K25" si="15">100*J9/J$16</f>
+        <v>4.3206014868392071</v>
+      </c>
+      <c r="K25" s="38">
+        <f t="shared" si="15"/>
+        <v>4.5112833589275061</v>
+      </c>
+      <c r="N25" s="38">
+        <f t="shared" si="3"/>
+        <v>404.79325201939997</v>
+      </c>
+      <c r="Q25" s="38">
+        <f t="shared" si="4"/>
+        <v>411.64526570603363</v>
+      </c>
+      <c r="T25" s="38">
+        <f t="shared" si="5"/>
+        <v>397.43481805950205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="6"/>
+        <v>55</v>
+      </c>
+      <c r="D26" s="38">
+        <f t="shared" ref="D26:E26" si="16">100*D10/D$16</f>
+        <v>3.050895850621218</v>
+      </c>
+      <c r="E26" s="38">
+        <f t="shared" si="16"/>
+        <v>3.3448416135337755</v>
+      </c>
+      <c r="G26" s="38">
+        <f t="shared" ref="G26:H26" si="17">100*G10/G$16</f>
+        <v>3.0710807716231581</v>
+      </c>
+      <c r="H26" s="38">
+        <f t="shared" si="17"/>
+        <v>3.3620616412817772</v>
+      </c>
+      <c r="J26" s="38">
+        <f t="shared" ref="J26:K26" si="18">100*J10/J$16</f>
+        <v>2.9324609655844216</v>
+      </c>
+      <c r="K26" s="38">
+        <f t="shared" si="18"/>
+        <v>3.2576641209841051</v>
+      </c>
+      <c r="N26" s="38">
+        <f t="shared" si="3"/>
+        <v>351.76556052852465</v>
+      </c>
+      <c r="Q26" s="38">
+        <f t="shared" si="4"/>
+        <v>353.82283270977143</v>
+      </c>
+      <c r="T26" s="38">
+        <f t="shared" si="5"/>
+        <v>340.45687976126897</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="6"/>
+        <v>65</v>
+      </c>
+      <c r="D27" s="38">
+        <f t="shared" ref="D27:E27" si="19">100*D11/D$16</f>
+        <v>1.8476749963633772</v>
+      </c>
+      <c r="E27" s="38">
+        <f t="shared" si="19"/>
+        <v>2.013734179894584</v>
+      </c>
+      <c r="G27" s="38">
+        <f t="shared" ref="G27:H27" si="20">100*G11/G$16</f>
+        <v>1.8299072280205626</v>
+      </c>
+      <c r="H27" s="38">
+        <f t="shared" si="20"/>
+        <v>2.0716355868869902</v>
+      </c>
+      <c r="J27" s="38">
+        <f t="shared" ref="J27:K27" si="21">100*J11/J$16</f>
+        <v>1.7432365614743512</v>
+      </c>
+      <c r="K27" s="38">
+        <f t="shared" si="21"/>
+        <v>2.0603969658886987</v>
+      </c>
+      <c r="N27" s="38">
+        <f t="shared" si="3"/>
+        <v>250.99159645676747</v>
+      </c>
+      <c r="Q27" s="38">
+        <f t="shared" si="4"/>
+        <v>253.60028296899094</v>
+      </c>
+      <c r="T27" s="38">
+        <f t="shared" si="5"/>
+        <v>247.23617927859823</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="6"/>
+        <v>75</v>
+      </c>
+      <c r="D28" s="38">
+        <f t="shared" ref="D28:E28" si="22">100*D12/D$16</f>
+        <v>0.6424886150625897</v>
+      </c>
+      <c r="E28" s="38">
+        <f t="shared" si="22"/>
+        <v>0.72271713185201025</v>
+      </c>
+      <c r="G28" s="38">
+        <f t="shared" ref="G28:H28" si="23">100*G12/G$16</f>
+        <v>0.73068774054895458</v>
+      </c>
+      <c r="H28" s="38">
+        <f t="shared" si="23"/>
+        <v>0.82971368098723952</v>
+      </c>
+      <c r="J28" s="38">
+        <f t="shared" ref="J28:K28" si="24">100*J12/J$16</f>
+        <v>0.69212560531936196</v>
+      </c>
+      <c r="K28" s="38">
+        <f t="shared" si="24"/>
+        <v>0.84909131441002128</v>
+      </c>
+      <c r="N28" s="38">
+        <f t="shared" si="3"/>
+        <v>102.390431018595</v>
+      </c>
+      <c r="Q28" s="38">
+        <f t="shared" si="4"/>
+        <v>117.03010661521456</v>
+      </c>
+      <c r="T28" s="38">
+        <f t="shared" si="5"/>
+        <v>115.59126897970374</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="B29">
+        <v>90</v>
+      </c>
+      <c r="D29" s="38">
+        <f t="shared" ref="D29:E29" si="25">100*D13/D$16</f>
+        <v>0.11937990566106801</v>
+      </c>
+      <c r="E29" s="38">
+        <f t="shared" si="25"/>
+        <v>0.1431890429586227</v>
+      </c>
+      <c r="G29" s="38">
+        <f t="shared" ref="G29:H29" si="26">100*G13/G$16</f>
+        <v>0.13128622495389133</v>
+      </c>
+      <c r="H29" s="38">
+        <f t="shared" si="26"/>
+        <v>0.16345846684630297</v>
+      </c>
+      <c r="J29" s="38">
+        <f t="shared" ref="J29:K29" si="27">100*J13/J$16</f>
+        <v>0.12987920289866556</v>
+      </c>
+      <c r="K29" s="38">
+        <f t="shared" si="27"/>
+        <v>0.16880532527843237</v>
+      </c>
+      <c r="N29" s="38">
+        <f t="shared" si="3"/>
+        <v>23.631205375772165</v>
+      </c>
+      <c r="Q29" s="38">
+        <f t="shared" si="4"/>
+        <v>26.527022262017486</v>
+      </c>
+      <c r="T29" s="38">
+        <f t="shared" si="5"/>
+        <v>26.881607535938812</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D30" s="38">
+        <f>SUM(D21:D29)</f>
+        <v>49.725462821936624</v>
+      </c>
+      <c r="E30" s="38">
+        <f>SUM(E21:E29)</f>
+        <v>50.274529220464011</v>
+      </c>
+      <c r="G30" s="38">
+        <f>SUM(G21:G29)</f>
+        <v>49.623023498135908</v>
+      </c>
+      <c r="H30" s="38">
+        <f>SUM(H21:H29)</f>
+        <v>50.376976501864078</v>
+      </c>
+      <c r="J30" s="38">
+        <f>SUM(J21:J29)</f>
+        <v>49.510673219197585</v>
+      </c>
+      <c r="K30" s="38">
+        <f>SUM(K21:K29)</f>
+        <v>50.489326780802422</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D31" s="38">
+        <f>D30+E30-100</f>
+        <v>-7.9575993652269972E-6</v>
+      </c>
+      <c r="G31" s="38">
+        <f>G30+H30-100</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="38">
+        <f>J30+K30-100</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="41">
+        <f>SUM(N21:N29) / 100</f>
+        <v>24.404241193563507</v>
+      </c>
+      <c r="Q31" s="41">
+        <f>SUM(Q21:Q29) / 100</f>
+        <v>24.55111431879735</v>
+      </c>
+      <c r="T31" s="41">
+        <f>SUM(T21:T29) / 100</f>
+        <v>24.242220652411053</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D35" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" s="32"/>
+      <c r="G35" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="K35" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="L35" s="40"/>
+      <c r="M35" s="40"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E36" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="10">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1799585</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1792949</v>
+      </c>
+      <c r="G37" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="H37" s="37">
+        <f>SUM(D37:D46)</f>
+        <v>13416156</v>
+      </c>
+      <c r="I37" s="37">
+        <f>SUM(E37:E46)</f>
+        <v>13585144</v>
+      </c>
+      <c r="K37" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="L37" s="38">
+        <f>H37/H$49*100</f>
+        <v>13.528830731458646</v>
+      </c>
+      <c r="M37" s="38">
+        <f>I37/I$49*100</f>
+        <v>13.699237966410873</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="10">
+        <v>1</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1430584</v>
+      </c>
+      <c r="E38" s="4">
+        <v>1450048</v>
+      </c>
+      <c r="G38" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="H38" s="9">
+        <f>SUM(D47:D56)</f>
+        <v>10341973</v>
+      </c>
+      <c r="I38" s="9">
+        <f>SUM(E47:E56)</f>
+        <v>10775804</v>
+      </c>
+      <c r="K38" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="L38" s="38">
+        <f t="shared" ref="L38:M45" si="28">H38/H$49*100</f>
+        <v>10.428829401381108</v>
+      </c>
+      <c r="M38" s="38">
+        <f t="shared" si="28"/>
+        <v>10.866303903396398</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="10">
+        <v>2</v>
+      </c>
+      <c r="D39" s="4">
+        <v>1450430</v>
+      </c>
+      <c r="E39" s="4">
+        <v>1460857</v>
+      </c>
+      <c r="G39" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="H39" s="9">
+        <f>SUM(D57:D66)</f>
+        <v>7645101</v>
+      </c>
+      <c r="I39" s="9">
+        <f>SUM(E57:E66)</f>
+        <v>8068598</v>
+      </c>
+      <c r="K39" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="L39" s="38">
+        <f t="shared" si="28"/>
+        <v>7.7093078936995978</v>
+      </c>
+      <c r="M39" s="38">
+        <f t="shared" si="28"/>
+        <v>8.1363616062742388</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="10">
+        <v>3</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1428134</v>
+      </c>
+      <c r="E40" s="4">
+        <v>1448117</v>
+      </c>
+      <c r="G40" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="H40" s="9">
+        <f>SUM(D67:D76)</f>
+        <v>6067167</v>
+      </c>
+      <c r="I40" s="9">
+        <f>SUM(E67:E76)</f>
+        <v>6248301</v>
+      </c>
+      <c r="K40" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="L40" s="38">
+        <f t="shared" si="28"/>
+        <v>6.1181217155265459</v>
+      </c>
+      <c r="M40" s="38">
+        <f t="shared" si="28"/>
+        <v>6.3007769578859838</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="10">
+        <v>4</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1331294</v>
+      </c>
+      <c r="E41" s="4">
+        <v>1363876</v>
+      </c>
+      <c r="G41" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="H41" s="9">
+        <f>SUM(D77:D86)</f>
+        <v>4628357</v>
+      </c>
+      <c r="I41" s="9">
+        <f>SUM(E77:E86)</f>
+        <v>4737341</v>
+      </c>
+      <c r="K41" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="L41" s="38">
+        <f t="shared" si="28"/>
+        <v>4.6672279614042758</v>
+      </c>
+      <c r="M41" s="38">
+        <f t="shared" si="28"/>
+        <v>4.7771272565851977</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="10">
+        <v>5</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1253530</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1269384</v>
+      </c>
+      <c r="G42" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="H42" s="9">
+        <f>SUM(D87:D96)</f>
+        <v>3236247</v>
+      </c>
+      <c r="I42" s="9">
+        <f>SUM(E87:E96)</f>
+        <v>3436004</v>
+      </c>
+      <c r="K42" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="L42" s="38">
+        <f t="shared" si="28"/>
+        <v>3.2634264142568745</v>
+      </c>
+      <c r="M42" s="38">
+        <f t="shared" si="28"/>
+        <v>3.4648610606953909</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="10">
+        <v>6</v>
+      </c>
+      <c r="D43" s="4">
+        <v>1232195</v>
+      </c>
+      <c r="E43" s="4">
+        <v>1247881</v>
+      </c>
+      <c r="G43" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" s="9">
+        <f>SUM(D97:D106)</f>
+        <v>2123010</v>
+      </c>
+      <c r="I43" s="9">
+        <f>SUM(E97:E106)</f>
+        <v>2264552</v>
+      </c>
+      <c r="K43" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="L43" s="38">
+        <f t="shared" si="28"/>
+        <v>2.140839964233721</v>
+      </c>
+      <c r="M43" s="38">
+        <f t="shared" si="28"/>
+        <v>2.2835706957034594</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="10">
+        <v>7</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1179192</v>
+      </c>
+      <c r="E44" s="4">
+        <v>1223008</v>
+      </c>
+      <c r="G44" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="H44" s="9">
+        <f>SUM(D107:D116)</f>
+        <v>930891</v>
+      </c>
+      <c r="I44" s="9">
+        <f>SUM(E107:E116)</f>
+        <v>1021278</v>
+      </c>
+      <c r="K44" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="L44" s="38">
+        <f t="shared" si="28"/>
+        <v>0.93870902875892848</v>
+      </c>
+      <c r="M44" s="38">
+        <f t="shared" si="28"/>
+        <v>1.0298551382201149</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="10">
+        <v>8</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1215578</v>
+      </c>
+      <c r="E45" s="4">
+        <v>1235027</v>
+      </c>
+      <c r="G45" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="H45" s="9">
+        <f>SUM(D117:D146)</f>
+        <v>307220</v>
+      </c>
+      <c r="I45" s="9">
+        <f>SUM(E117:E146)</f>
+        <v>334007</v>
+      </c>
+      <c r="K45" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="L45" s="38">
+        <f t="shared" si="28"/>
+        <v>0.30980016759783691</v>
+      </c>
+      <c r="M45" s="38">
+        <f t="shared" si="28"/>
+        <v>0.33681213651080893</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="10">
+        <v>9</v>
+      </c>
+      <c r="D46" s="4">
+        <v>1095634</v>
+      </c>
+      <c r="E46" s="4">
+        <v>1093997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="10">
+        <v>10</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1204078</v>
+      </c>
+      <c r="E47" s="4">
+        <v>1215355</v>
+      </c>
+      <c r="G47" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="4">
+        <f>SUM(H37:H45)</f>
+        <v>48696122</v>
+      </c>
+      <c r="I47" s="4">
+        <f>SUM(I37:I45)</f>
+        <v>50471029</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="10">
+        <v>11</v>
+      </c>
+      <c r="D48" s="4">
+        <v>981933</v>
+      </c>
+      <c r="E48" s="4">
+        <v>969224</v>
+      </c>
+      <c r="G48" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="H48" s="4">
+        <f>H47-D148</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="4">
+        <f>I47-E148</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="10">
+        <v>12</v>
+      </c>
+      <c r="D49" s="4">
+        <v>1276307</v>
+      </c>
+      <c r="E49" s="4">
+        <v>1281067</v>
+      </c>
+      <c r="G49" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" s="4">
+        <f>H47+I47</f>
+        <v>99167151</v>
+      </c>
+      <c r="I49" s="4">
+        <f>H49</f>
+        <v>99167151</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="10">
+        <v>13</v>
+      </c>
+      <c r="D50" s="4">
+        <v>1052707</v>
+      </c>
+      <c r="E50" s="4">
+        <v>1058899</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="10">
+        <v>14</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1023946</v>
+      </c>
+      <c r="E51" s="4">
+        <v>1049048</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="10">
+        <v>15</v>
+      </c>
+      <c r="D52" s="4">
+        <v>992837</v>
+      </c>
+      <c r="E52" s="4">
+        <v>1022042</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="10">
+        <v>16</v>
+      </c>
+      <c r="D53" s="4">
+        <v>984612</v>
+      </c>
+      <c r="E53" s="4">
+        <v>1094871</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="10">
+        <v>17</v>
+      </c>
+      <c r="D54" s="4">
+        <v>978629</v>
+      </c>
+      <c r="E54" s="4">
+        <v>1098460</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="10">
+        <v>18</v>
+      </c>
+      <c r="D55" s="4">
+        <v>998723</v>
+      </c>
+      <c r="E55" s="4">
+        <v>1089350</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="10">
+        <v>19</v>
+      </c>
+      <c r="D56" s="4">
+        <v>848201</v>
+      </c>
+      <c r="E56" s="4">
+        <v>897488</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="10">
+        <v>20</v>
+      </c>
+      <c r="D57" s="4">
+        <v>879164</v>
+      </c>
+      <c r="E57" s="4">
+        <v>1192042</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="10">
+        <v>21</v>
+      </c>
+      <c r="D58" s="4">
+        <v>800179</v>
+      </c>
+      <c r="E58" s="4">
+        <v>636809</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="10">
+        <v>22</v>
+      </c>
+      <c r="D59" s="4">
+        <v>863687</v>
+      </c>
+      <c r="E59" s="4">
+        <v>885528</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="10">
+        <v>23</v>
+      </c>
+      <c r="D60" s="4">
+        <v>791814</v>
+      </c>
+      <c r="E60" s="4">
+        <v>825830</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="10">
+        <v>24</v>
+      </c>
+      <c r="D61" s="4">
+        <v>690732</v>
+      </c>
+      <c r="E61" s="4">
+        <v>720216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="10">
+        <v>25</v>
+      </c>
+      <c r="D62" s="4">
+        <v>795114</v>
+      </c>
+      <c r="E62" s="4">
+        <v>1072869</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="10">
+        <v>26</v>
+      </c>
+      <c r="D63" s="4">
+        <v>748462</v>
+      </c>
+      <c r="E63" s="4">
+        <v>727473</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="10">
+        <v>27</v>
+      </c>
+      <c r="D64" s="4">
+        <v>785934</v>
+      </c>
+      <c r="E64" s="4">
+        <v>760804</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
+        <v>28</v>
+      </c>
+      <c r="D65" s="4">
+        <v>785014</v>
+      </c>
+      <c r="E65" s="4">
+        <v>807738</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="10">
+        <v>29</v>
+      </c>
+      <c r="D66" s="4">
+        <v>505001</v>
+      </c>
+      <c r="E66" s="4">
+        <v>439289</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="10">
+        <v>30</v>
+      </c>
+      <c r="D67" s="4">
+        <v>1055694</v>
+      </c>
+      <c r="E67" s="4">
+        <v>1376799</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="10">
+        <v>31</v>
+      </c>
+      <c r="D68" s="4">
+        <v>401717</v>
+      </c>
+      <c r="E68" s="4">
+        <v>339826</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="10">
+        <v>32</v>
+      </c>
+      <c r="D69" s="4">
+        <v>602761</v>
+      </c>
+      <c r="E69" s="4">
+        <v>581295</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="10">
+        <v>33</v>
+      </c>
+      <c r="D70" s="4">
+        <v>573913</v>
+      </c>
+      <c r="E70" s="4">
+        <v>527699</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="10">
+        <v>34</v>
+      </c>
+      <c r="D71" s="4">
+        <v>431960</v>
+      </c>
+      <c r="E71" s="4">
+        <v>437786</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="10">
+        <v>35</v>
+      </c>
+      <c r="D72" s="4">
+        <v>813420</v>
+      </c>
+      <c r="E72" s="4">
+        <v>952338</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="10">
+        <v>36</v>
+      </c>
+      <c r="D73" s="4">
+        <v>570698</v>
+      </c>
+      <c r="E73" s="4">
+        <v>543752</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="10">
+        <v>37</v>
+      </c>
+      <c r="D74" s="4">
+        <v>584686</v>
+      </c>
+      <c r="E74" s="4">
+        <v>542612</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="10">
+        <v>38</v>
+      </c>
+      <c r="D75" s="4">
+        <v>632533</v>
+      </c>
+      <c r="E75" s="4">
+        <v>605566</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="10">
+        <v>39</v>
+      </c>
+      <c r="D76" s="4">
+        <v>399785</v>
+      </c>
+      <c r="E76" s="4">
+        <v>340628</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="10">
+        <v>40</v>
+      </c>
+      <c r="D77" s="4">
+        <v>905505</v>
+      </c>
+      <c r="E77" s="4">
+        <v>1199144</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="10">
+        <v>41</v>
+      </c>
+      <c r="D78" s="4">
+        <v>308069</v>
+      </c>
+      <c r="E78" s="4">
+        <v>256184</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="10">
+        <v>42</v>
+      </c>
+      <c r="D79" s="4">
+        <v>503889</v>
+      </c>
+      <c r="E79" s="4">
+        <v>452626</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="10">
+        <v>43</v>
+      </c>
+      <c r="D80" s="4">
+        <v>423710</v>
+      </c>
+      <c r="E80" s="4">
+        <v>385797</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="10">
+        <v>44</v>
+      </c>
+      <c r="D81" s="4">
+        <v>341645</v>
+      </c>
+      <c r="E81" s="4">
+        <v>328233</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="10">
+        <v>45</v>
+      </c>
+      <c r="D82" s="4">
+        <v>715609</v>
+      </c>
+      <c r="E82" s="4">
+        <v>796360</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="10">
+        <v>46</v>
+      </c>
+      <c r="D83" s="4">
+        <v>383680</v>
+      </c>
+      <c r="E83" s="4">
+        <v>340053</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="10">
+        <v>47</v>
+      </c>
+      <c r="D84" s="4">
+        <v>360612</v>
+      </c>
+      <c r="E84" s="4">
+        <v>335352</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="10">
+        <v>48</v>
+      </c>
+      <c r="D85" s="4">
+        <v>440852</v>
+      </c>
+      <c r="E85" s="4">
+        <v>419733</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="10">
+        <v>49</v>
+      </c>
+      <c r="D86" s="4">
+        <v>244786</v>
+      </c>
+      <c r="E86" s="4">
+        <v>223859</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="10">
+        <v>50</v>
+      </c>
+      <c r="D87" s="4">
+        <v>812835</v>
+      </c>
+      <c r="E87" s="4">
+        <v>1082324</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="10">
+        <v>51</v>
+      </c>
+      <c r="D88" s="4">
+        <v>183378</v>
+      </c>
+      <c r="E88" s="4">
+        <v>170897</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="10">
+        <v>52</v>
+      </c>
+      <c r="D89" s="4">
+        <v>313188</v>
+      </c>
+      <c r="E89" s="4">
+        <v>295658</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="10">
+        <v>53</v>
+      </c>
+      <c r="D90" s="4">
+        <v>259360</v>
+      </c>
+      <c r="E90" s="4">
+        <v>253700</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="10">
+        <v>54</v>
+      </c>
+      <c r="D91" s="4">
+        <v>210742</v>
+      </c>
+      <c r="E91" s="4">
+        <v>222184</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="10">
+        <v>55</v>
+      </c>
+      <c r="D92" s="4">
+        <v>542450</v>
+      </c>
+      <c r="E92" s="4">
+        <v>585136</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="10">
+        <v>56</v>
+      </c>
+      <c r="D93" s="4">
+        <v>288780</v>
+      </c>
+      <c r="E93" s="4">
+        <v>258577</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="10">
+        <v>57</v>
+      </c>
+      <c r="D94" s="4">
+        <v>232543</v>
+      </c>
+      <c r="E94" s="4">
+        <v>208310</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="10">
+        <v>58</v>
+      </c>
+      <c r="D95" s="4">
+        <v>252281</v>
+      </c>
+      <c r="E95" s="4">
+        <v>233912</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="10">
+        <v>59</v>
+      </c>
+      <c r="D96" s="4">
+        <v>140690</v>
+      </c>
+      <c r="E96" s="4">
+        <v>125306</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="10">
+        <v>60</v>
+      </c>
+      <c r="D97" s="4">
+        <v>686050</v>
+      </c>
+      <c r="E97" s="4">
+        <v>907775</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="10">
+        <v>61</v>
+      </c>
+      <c r="D98" s="4">
+        <v>118251</v>
+      </c>
+      <c r="E98" s="4">
+        <v>102415</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="10">
+        <v>62</v>
+      </c>
+      <c r="D99" s="4">
+        <v>197306</v>
+      </c>
+      <c r="E99" s="4">
+        <v>177053</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="10">
+        <v>63</v>
+      </c>
+      <c r="D100" s="4">
+        <v>176982</v>
+      </c>
+      <c r="E100" s="4">
+        <v>158971</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="10">
+        <v>64</v>
+      </c>
+      <c r="D101" s="4">
+        <v>122679</v>
+      </c>
+      <c r="E101" s="4">
+        <v>117725</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="10">
+        <v>65</v>
+      </c>
+      <c r="D102" s="4">
+        <v>357326</v>
+      </c>
+      <c r="E102" s="4">
+        <v>390908</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="10">
+        <v>66</v>
+      </c>
+      <c r="D103" s="4">
+        <v>140457</v>
+      </c>
+      <c r="E103" s="4">
+        <v>113437</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="10">
+        <v>67</v>
+      </c>
+      <c r="D104" s="4">
+        <v>148740</v>
+      </c>
+      <c r="E104" s="4">
+        <v>127023</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="10">
+        <v>68</v>
+      </c>
+      <c r="D105" s="4">
+        <v>114114</v>
+      </c>
+      <c r="E105" s="4">
+        <v>108737</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="10">
+        <v>69</v>
+      </c>
+      <c r="D106" s="4">
+        <v>61105</v>
+      </c>
+      <c r="E106" s="4">
+        <v>60508</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="10">
+        <v>70</v>
+      </c>
+      <c r="D107" s="4">
+        <v>379260</v>
+      </c>
+      <c r="E107" s="4">
+        <v>522328</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="10">
+        <v>71</v>
+      </c>
+      <c r="D108" s="4">
+        <v>47362</v>
+      </c>
+      <c r="E108" s="4">
+        <v>43292</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="10">
+        <v>72</v>
+      </c>
+      <c r="D109" s="4">
+        <v>80630</v>
+      </c>
+      <c r="E109" s="4">
+        <v>71854</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="10">
+        <v>73</v>
+      </c>
+      <c r="D110" s="4">
+        <v>62901</v>
+      </c>
+      <c r="E110" s="4">
+        <v>55974</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="10">
+        <v>74</v>
+      </c>
+      <c r="D111" s="4">
+        <v>46340</v>
+      </c>
+      <c r="E111" s="4">
+        <v>41171</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="10">
+        <v>75</v>
+      </c>
+      <c r="D112" s="4">
+        <v>158782</v>
+      </c>
+      <c r="E112" s="4">
+        <v>159422</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="10">
+        <v>76</v>
+      </c>
+      <c r="D113" s="4">
+        <v>49674</v>
+      </c>
+      <c r="E113" s="4">
+        <v>39445</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="10">
+        <v>77</v>
+      </c>
+      <c r="D114" s="4">
+        <v>40825</v>
+      </c>
+      <c r="E114" s="4">
+        <v>31463</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="10">
+        <v>78</v>
+      </c>
+      <c r="D115" s="4">
+        <v>46067</v>
+      </c>
+      <c r="E115" s="4">
+        <v>39379</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="10">
+        <v>79</v>
+      </c>
+      <c r="D116" s="4">
+        <v>19050</v>
+      </c>
+      <c r="E116" s="4">
+        <v>16950</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="10">
+        <v>80</v>
+      </c>
+      <c r="D117" s="4">
+        <v>141367</v>
+      </c>
+      <c r="E117" s="4">
+        <v>175101</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="10">
+        <v>81</v>
+      </c>
+      <c r="D118" s="4">
+        <v>12177</v>
+      </c>
+      <c r="E118" s="4">
+        <v>10458</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="10">
+        <v>82</v>
+      </c>
+      <c r="D119" s="4">
+        <v>18053</v>
+      </c>
+      <c r="E119" s="4">
+        <v>15247</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="10">
+        <v>83</v>
+      </c>
+      <c r="D120" s="4">
+        <v>13146</v>
+      </c>
+      <c r="E120" s="4">
+        <v>10975</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="10">
+        <v>84</v>
+      </c>
+      <c r="D121" s="4">
+        <v>11994</v>
+      </c>
+      <c r="E121" s="4">
+        <v>9312</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="10">
+        <v>85</v>
+      </c>
+      <c r="D122" s="4">
+        <v>36446</v>
+      </c>
+      <c r="E122" s="4">
+        <v>34885</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="10">
+        <v>86</v>
+      </c>
+      <c r="D123" s="4">
+        <v>9657</v>
+      </c>
+      <c r="E123" s="4">
+        <v>7264</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="10">
+        <v>87</v>
+      </c>
+      <c r="D124" s="4">
+        <v>7869</v>
+      </c>
+      <c r="E124" s="4">
+        <v>6388</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="10">
+        <v>88</v>
+      </c>
+      <c r="D125" s="4">
+        <v>6313</v>
+      </c>
+      <c r="E125" s="4">
+        <v>5342</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="10">
+        <v>89</v>
+      </c>
+      <c r="D126" s="4">
+        <v>3735</v>
+      </c>
+      <c r="E126" s="4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="10">
+        <v>90</v>
+      </c>
+      <c r="D127" s="4">
+        <v>24476</v>
+      </c>
+      <c r="E127" s="4">
+        <v>32625</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="10">
+        <v>91</v>
+      </c>
+      <c r="D128" s="4">
+        <v>1560</v>
+      </c>
+      <c r="E128" s="4">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="10">
+        <v>92</v>
+      </c>
+      <c r="D129" s="4">
+        <v>1941</v>
+      </c>
+      <c r="E129" s="4">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="10">
+        <v>93</v>
+      </c>
+      <c r="D130" s="4">
+        <v>1670</v>
+      </c>
+      <c r="E130" s="4">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="10">
+        <v>94</v>
+      </c>
+      <c r="D131" s="4">
+        <v>1391</v>
+      </c>
+      <c r="E131" s="4">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="10">
+        <v>95</v>
+      </c>
+      <c r="D132" s="4">
+        <v>5244</v>
+      </c>
+      <c r="E132" s="4">
+        <v>5745</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="10">
+        <v>96</v>
+      </c>
+      <c r="D133" s="4">
+        <v>2154</v>
+      </c>
+      <c r="E133" s="4">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="10">
+        <v>97</v>
+      </c>
+      <c r="D134" s="4">
+        <v>1638</v>
+      </c>
+      <c r="E134" s="4">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="10">
+        <v>98</v>
+      </c>
+      <c r="D135" s="4">
+        <v>1583</v>
+      </c>
+      <c r="E135" s="4">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="10">
+        <v>99</v>
+      </c>
+      <c r="D136" s="4">
+        <v>717</v>
+      </c>
+      <c r="E136" s="4">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="10">
+        <v>100</v>
+      </c>
+      <c r="D137" s="4">
+        <v>2400</v>
+      </c>
+      <c r="E137" s="4">
+        <v>3635</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="10">
+        <v>101</v>
+      </c>
+      <c r="D138" s="4">
+        <v>271</v>
+      </c>
+      <c r="E138" s="4">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="10">
+        <v>102</v>
+      </c>
+      <c r="D139" s="4">
+        <v>352</v>
+      </c>
+      <c r="E139" s="4">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="10">
+        <v>103</v>
+      </c>
+      <c r="D140" s="4">
+        <v>255</v>
+      </c>
+      <c r="E140" s="4">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="10">
+        <v>104</v>
+      </c>
+      <c r="D141" s="4">
+        <v>149</v>
+      </c>
+      <c r="E141" s="4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="10">
+        <v>105</v>
+      </c>
+      <c r="D142" s="4">
+        <v>318</v>
+      </c>
+      <c r="E142" s="4">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="10">
+        <v>106</v>
+      </c>
+      <c r="D143" s="4">
+        <v>115</v>
+      </c>
+      <c r="E143" s="4">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="10">
+        <v>107</v>
+      </c>
+      <c r="D144" s="4">
+        <v>91</v>
+      </c>
+      <c r="E144" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="10">
+        <v>108</v>
+      </c>
+      <c r="D145" s="4">
+        <v>61</v>
+      </c>
+      <c r="E145" s="4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="10">
+        <v>109</v>
+      </c>
+      <c r="D146" s="4">
+        <v>77</v>
+      </c>
+      <c r="E146" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" s="4">
+        <f>SUM(D37:D146)</f>
+        <v>48696122</v>
+      </c>
+      <c r="E148" s="4">
+        <f>SUM(E37:E146)</f>
+        <v>50471029</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="N18:T18"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="K35:M35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="H37:H43 H44:H45" formulaRange="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61615065-1ECC-43AC-8405-EDEEC798E5A5}">
+  <dimension ref="A1:N38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="D4" s="38">
+        <v>14.785951717743314</v>
+      </c>
+      <c r="E4" s="38">
+        <v>14.450658268534601</v>
+      </c>
+      <c r="G4" s="38">
+        <v>14.853729654266891</v>
+      </c>
+      <c r="H4" s="38">
+        <v>14.50429581969223</v>
+      </c>
+      <c r="J4" s="38">
+        <v>15.11217722683833</v>
+      </c>
+      <c r="K4" s="38">
+        <v>14.777359748421693</v>
+      </c>
+      <c r="M4" s="38">
+        <v>13.528830731458646</v>
+      </c>
+      <c r="N4" s="38">
+        <v>13.699237966410873</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="D5" s="38">
+        <v>10.57322248715723</v>
+      </c>
+      <c r="E5" s="38">
+        <v>10.442614408793338</v>
+      </c>
+      <c r="G5" s="38">
+        <v>10.431289996112918</v>
+      </c>
+      <c r="H5" s="38">
+        <v>10.455611770770465</v>
+      </c>
+      <c r="J5" s="38">
+        <v>10.506361829235889</v>
+      </c>
+      <c r="K5" s="38">
+        <v>10.553106192310761</v>
+      </c>
+      <c r="M5" s="38">
+        <v>10.428829401381108</v>
+      </c>
+      <c r="N5" s="38">
+        <v>10.866303903396398</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>25</v>
+      </c>
+      <c r="D6" s="38">
+        <v>8.1745553532203292</v>
+      </c>
+      <c r="E6" s="38">
+        <v>8.3175613713935768</v>
+      </c>
+      <c r="G6" s="38">
+        <v>8.0908162593007855</v>
+      </c>
+      <c r="H6" s="38">
+        <v>8.1314479299051587</v>
+      </c>
+      <c r="J6" s="38">
+        <v>8.1018632241051147</v>
+      </c>
+      <c r="K6" s="38">
+        <v>8.1190514677954511</v>
+      </c>
+      <c r="M6" s="38">
+        <v>7.7093078936995978</v>
+      </c>
+      <c r="N6" s="38">
+        <v>8.1363616062742388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>35</v>
+      </c>
+      <c r="D7" s="38">
+        <v>6.1251154249787767</v>
+      </c>
+      <c r="E7" s="38">
+        <v>6.2499860742011126</v>
+      </c>
+      <c r="G7" s="38">
+        <v>5.9921369133224776</v>
+      </c>
+      <c r="H7" s="38">
+        <v>6.2031677442350057</v>
+      </c>
+      <c r="J7" s="38">
+        <v>5.9719671169022437</v>
+      </c>
+      <c r="K7" s="38">
+        <v>6.1925682867857468</v>
+      </c>
+      <c r="M7" s="38">
+        <v>6.1181217155265459</v>
+      </c>
+      <c r="N7" s="38">
+        <v>6.3007769578859838</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>45</v>
+      </c>
+      <c r="D8" s="38">
+        <v>4.4061784711287153</v>
+      </c>
+      <c r="E8" s="38">
+        <v>4.5892271293023956</v>
+      </c>
+      <c r="G8" s="38">
+        <v>4.4920887099862785</v>
+      </c>
+      <c r="H8" s="38">
+        <v>4.6555838612589131</v>
+      </c>
+      <c r="J8" s="38">
+        <v>4.3206014868392071</v>
+      </c>
+      <c r="K8" s="38">
+        <v>4.5112833589275061</v>
+      </c>
+      <c r="M8" s="38">
+        <v>4.6672279614042758</v>
+      </c>
+      <c r="N8" s="38">
+        <v>4.7771272565851977</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>55</v>
+      </c>
+      <c r="D9" s="38">
+        <v>3.050895850621218</v>
+      </c>
+      <c r="E9" s="38">
+        <v>3.3448416135337755</v>
+      </c>
+      <c r="G9" s="38">
+        <v>3.0710807716231581</v>
+      </c>
+      <c r="H9" s="38">
+        <v>3.3620616412817772</v>
+      </c>
+      <c r="J9" s="38">
+        <v>2.9324609655844216</v>
+      </c>
+      <c r="K9" s="38">
+        <v>3.2576641209841051</v>
+      </c>
+      <c r="M9" s="38">
+        <v>3.2634264142568745</v>
+      </c>
+      <c r="N9" s="38">
+        <v>3.4648610606953909</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>65</v>
+      </c>
+      <c r="D10" s="38">
+        <v>1.8476749963633772</v>
+      </c>
+      <c r="E10" s="38">
+        <v>2.013734179894584</v>
+      </c>
+      <c r="G10" s="38">
+        <v>1.8299072280205626</v>
+      </c>
+      <c r="H10" s="38">
+        <v>2.0716355868869902</v>
+      </c>
+      <c r="J10" s="38">
+        <v>1.7432365614743512</v>
+      </c>
+      <c r="K10" s="38">
+        <v>2.0603969658886987</v>
+      </c>
+      <c r="M10" s="38">
+        <v>2.140839964233721</v>
+      </c>
+      <c r="N10" s="38">
+        <v>2.2835706957034594</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11">
+        <v>75</v>
+      </c>
+      <c r="D11" s="38">
+        <v>0.6424886150625897</v>
+      </c>
+      <c r="E11" s="38">
+        <v>0.72271713185201025</v>
+      </c>
+      <c r="G11" s="38">
+        <v>0.73068774054895458</v>
+      </c>
+      <c r="H11" s="38">
+        <v>0.82971368098723952</v>
+      </c>
+      <c r="J11" s="38">
+        <v>0.69212560531936196</v>
+      </c>
+      <c r="K11" s="38">
+        <v>0.84909131441002128</v>
+      </c>
+      <c r="M11" s="38">
+        <v>0.93870902875892848</v>
+      </c>
+      <c r="N11" s="38">
+        <v>1.0298551382201149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12">
+        <v>90</v>
+      </c>
+      <c r="D12" s="38">
+        <v>0.11937990566106801</v>
+      </c>
+      <c r="E12" s="38">
+        <v>0.1431890429586227</v>
+      </c>
+      <c r="G12" s="38">
+        <v>0.13128622495389133</v>
+      </c>
+      <c r="H12" s="38">
+        <v>0.16345846684630297</v>
+      </c>
+      <c r="J12" s="38">
+        <v>0.12987920289866556</v>
+      </c>
+      <c r="K12" s="38">
+        <v>0.16880532527843237</v>
+      </c>
+      <c r="M12" s="38">
+        <v>0.30980016759783691</v>
+      </c>
+      <c r="N12" s="38">
+        <v>0.33681213651080893</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="D18" s="38">
+        <f>D4/10</f>
+        <v>1.4785951717743315</v>
+      </c>
+      <c r="E18" s="38">
+        <f>E4/10</f>
+        <v>1.4450658268534602</v>
+      </c>
+      <c r="G18" s="38">
+        <f>G4/10</f>
+        <v>1.4853729654266892</v>
+      </c>
+      <c r="H18" s="38">
+        <f>H4/10</f>
+        <v>1.450429581969223</v>
+      </c>
+      <c r="J18" s="38">
+        <f>J4/10</f>
+        <v>1.511217722683833</v>
+      </c>
+      <c r="K18" s="38">
+        <f>K4/10</f>
+        <v>1.4777359748421692</v>
+      </c>
+      <c r="M18" s="38">
+        <f>M4/10</f>
+        <v>1.3528830731458645</v>
+      </c>
+      <c r="N18" s="38">
+        <f>N4/10</f>
+        <v>1.3699237966410873</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="D19" s="38">
+        <f t="shared" ref="D19:E19" si="0">D5/10</f>
+        <v>1.057322248715723</v>
+      </c>
+      <c r="E19" s="38">
+        <f t="shared" si="0"/>
+        <v>1.0442614408793338</v>
+      </c>
+      <c r="G19" s="38">
+        <f t="shared" ref="G19:H19" si="1">G5/10</f>
+        <v>1.0431289996112918</v>
+      </c>
+      <c r="H19" s="38">
+        <f t="shared" si="1"/>
+        <v>1.0455611770770465</v>
+      </c>
+      <c r="J19" s="38">
+        <f t="shared" ref="J19:K19" si="2">J5/10</f>
+        <v>1.0506361829235888</v>
+      </c>
+      <c r="K19" s="38">
+        <f t="shared" si="2"/>
+        <v>1.0553106192310762</v>
+      </c>
+      <c r="M19" s="38">
+        <f t="shared" ref="M19:N19" si="3">M5/10</f>
+        <v>1.0428829401381108</v>
+      </c>
+      <c r="N19" s="38">
+        <f t="shared" si="3"/>
+        <v>1.0866303903396397</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>25</v>
+      </c>
+      <c r="D20" s="38">
+        <f t="shared" ref="D20:E20" si="4">D6/10</f>
+        <v>0.81745553532203297</v>
+      </c>
+      <c r="E20" s="38">
+        <f t="shared" si="4"/>
+        <v>0.8317561371393577</v>
+      </c>
+      <c r="G20" s="38">
+        <f t="shared" ref="G20:H20" si="5">G6/10</f>
+        <v>0.8090816259300786</v>
+      </c>
+      <c r="H20" s="38">
+        <f t="shared" si="5"/>
+        <v>0.8131447929905159</v>
+      </c>
+      <c r="J20" s="38">
+        <f t="shared" ref="J20:K20" si="6">J6/10</f>
+        <v>0.81018632241051147</v>
+      </c>
+      <c r="K20" s="38">
+        <f t="shared" si="6"/>
+        <v>0.81190514677954506</v>
+      </c>
+      <c r="M20" s="38">
+        <f t="shared" ref="M20:N20" si="7">M6/10</f>
+        <v>0.77093078936995973</v>
+      </c>
+      <c r="N20" s="38">
+        <f t="shared" si="7"/>
+        <v>0.81363616062742383</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>35</v>
+      </c>
+      <c r="D21" s="38">
+        <f t="shared" ref="D21:E21" si="8">D7/10</f>
+        <v>0.61251154249787765</v>
+      </c>
+      <c r="E21" s="38">
+        <f t="shared" si="8"/>
+        <v>0.62499860742011126</v>
+      </c>
+      <c r="G21" s="38">
+        <f t="shared" ref="G21:H21" si="9">G7/10</f>
+        <v>0.59921369133224778</v>
+      </c>
+      <c r="H21" s="38">
+        <f t="shared" si="9"/>
+        <v>0.62031677442350053</v>
+      </c>
+      <c r="J21" s="38">
+        <f t="shared" ref="J21:K21" si="10">J7/10</f>
+        <v>0.59719671169022437</v>
+      </c>
+      <c r="K21" s="38">
+        <f t="shared" si="10"/>
+        <v>0.61925682867857468</v>
+      </c>
+      <c r="M21" s="38">
+        <f t="shared" ref="M21:N21" si="11">M7/10</f>
+        <v>0.61181217155265455</v>
+      </c>
+      <c r="N21" s="38">
+        <f t="shared" si="11"/>
+        <v>0.6300776957885984</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22">
+        <v>45</v>
+      </c>
+      <c r="D22" s="38">
+        <f t="shared" ref="D22:E22" si="12">D8/10</f>
+        <v>0.44061784711287155</v>
+      </c>
+      <c r="E22" s="38">
+        <f t="shared" si="12"/>
+        <v>0.45892271293023956</v>
+      </c>
+      <c r="G22" s="38">
+        <f t="shared" ref="G22:H22" si="13">G8/10</f>
+        <v>0.44920887099862783</v>
+      </c>
+      <c r="H22" s="38">
+        <f t="shared" si="13"/>
+        <v>0.46555838612589129</v>
+      </c>
+      <c r="J22" s="38">
+        <f t="shared" ref="J22:K22" si="14">J8/10</f>
+        <v>0.43206014868392073</v>
+      </c>
+      <c r="K22" s="38">
+        <f t="shared" si="14"/>
+        <v>0.45112833589275059</v>
+      </c>
+      <c r="M22" s="38">
+        <f t="shared" ref="M22:N22" si="15">M8/10</f>
+        <v>0.46672279614042755</v>
+      </c>
+      <c r="N22" s="38">
+        <f t="shared" si="15"/>
+        <v>0.47771272565851974</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23">
+        <v>55</v>
+      </c>
+      <c r="D23" s="38">
+        <f t="shared" ref="D23:E23" si="16">D9/10</f>
+        <v>0.3050895850621218</v>
+      </c>
+      <c r="E23" s="38">
+        <f t="shared" si="16"/>
+        <v>0.33448416135337755</v>
+      </c>
+      <c r="G23" s="38">
+        <f t="shared" ref="G23:H23" si="17">G9/10</f>
+        <v>0.30710807716231581</v>
+      </c>
+      <c r="H23" s="38">
+        <f t="shared" si="17"/>
+        <v>0.33620616412817772</v>
+      </c>
+      <c r="J23" s="38">
+        <f t="shared" ref="J23:K23" si="18">J9/10</f>
+        <v>0.29324609655844214</v>
+      </c>
+      <c r="K23" s="38">
+        <f t="shared" si="18"/>
+        <v>0.32576641209841051</v>
+      </c>
+      <c r="M23" s="38">
+        <f t="shared" ref="M23:N23" si="19">M9/10</f>
+        <v>0.32634264142568747</v>
+      </c>
+      <c r="N23" s="38">
+        <f t="shared" si="19"/>
+        <v>0.34648610606953911</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24">
+        <v>65</v>
+      </c>
+      <c r="D24" s="38">
+        <f t="shared" ref="D24:E24" si="20">D10/10</f>
+        <v>0.18476749963633771</v>
+      </c>
+      <c r="E24" s="38">
+        <f t="shared" si="20"/>
+        <v>0.2013734179894584</v>
+      </c>
+      <c r="G24" s="38">
+        <f t="shared" ref="G24:H24" si="21">G10/10</f>
+        <v>0.18299072280205625</v>
+      </c>
+      <c r="H24" s="38">
+        <f t="shared" si="21"/>
+        <v>0.20716355868869901</v>
+      </c>
+      <c r="J24" s="38">
+        <f t="shared" ref="J24:K24" si="22">J10/10</f>
+        <v>0.17432365614743511</v>
+      </c>
+      <c r="K24" s="38">
+        <f t="shared" si="22"/>
+        <v>0.20603969658886986</v>
+      </c>
+      <c r="M24" s="38">
+        <f t="shared" ref="M24:N24" si="23">M10/10</f>
+        <v>0.21408399642337211</v>
+      </c>
+      <c r="N24" s="38">
+        <f t="shared" si="23"/>
+        <v>0.22835706957034593</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B25">
+        <v>75</v>
+      </c>
+      <c r="D25" s="38">
+        <f t="shared" ref="D25:E25" si="24">D11/10</f>
+        <v>6.424886150625897E-2</v>
+      </c>
+      <c r="E25" s="38">
+        <f t="shared" si="24"/>
+        <v>7.2271713185201023E-2</v>
+      </c>
+      <c r="G25" s="38">
+        <f t="shared" ref="G25:H25" si="25">G11/10</f>
+        <v>7.3068774054895452E-2</v>
+      </c>
+      <c r="H25" s="38">
+        <f t="shared" si="25"/>
+        <v>8.2971368098723949E-2</v>
+      </c>
+      <c r="J25" s="38">
+        <f t="shared" ref="J25:K25" si="26">J11/10</f>
+        <v>6.9212560531936196E-2</v>
+      </c>
+      <c r="K25" s="38">
+        <f t="shared" si="26"/>
+        <v>8.4909131441002123E-2</v>
+      </c>
+      <c r="M25" s="38">
+        <f t="shared" ref="M25:N25" si="27">M11/10</f>
+        <v>9.387090287589285E-2</v>
+      </c>
+      <c r="N25" s="38">
+        <f t="shared" si="27"/>
+        <v>0.10298551382201149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B26">
+        <v>90</v>
+      </c>
+      <c r="D26" s="38">
+        <f t="shared" ref="D26:E26" si="28">D12/10</f>
+        <v>1.1937990566106801E-2</v>
+      </c>
+      <c r="E26" s="38">
+        <f t="shared" si="28"/>
+        <v>1.4318904295862269E-2</v>
+      </c>
+      <c r="G26" s="38">
+        <f t="shared" ref="G26:H26" si="29">G12/10</f>
+        <v>1.3128622495389134E-2</v>
+      </c>
+      <c r="H26" s="38">
+        <f t="shared" si="29"/>
+        <v>1.6345846684630298E-2</v>
+      </c>
+      <c r="J26" s="38">
+        <f t="shared" ref="J26:K26" si="30">J12/10</f>
+        <v>1.2987920289866556E-2</v>
+      </c>
+      <c r="K26" s="38">
+        <f t="shared" si="30"/>
+        <v>1.6880532527843238E-2</v>
+      </c>
+      <c r="M26" s="38">
+        <f t="shared" ref="M26:N26" si="31">M12/10</f>
+        <v>3.098001675978369E-2</v>
+      </c>
+      <c r="N26" s="38">
+        <f t="shared" si="31"/>
+        <v>3.3681213651080892E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>5</v>
+      </c>
+      <c r="B30" s="38">
+        <f>D18</f>
+        <v>1.4785951717743315</v>
+      </c>
+      <c r="C30" s="38">
+        <f>G18</f>
+        <v>1.4853729654266892</v>
+      </c>
+      <c r="D30" s="38">
+        <f>J18</f>
+        <v>1.511217722683833</v>
+      </c>
+      <c r="E30" s="38">
+        <f>M18</f>
+        <v>1.3528830731458645</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="I30" s="38">
+        <f>E18</f>
+        <v>1.4450658268534602</v>
+      </c>
+      <c r="J30" s="38">
+        <f>H18</f>
+        <v>1.450429581969223</v>
+      </c>
+      <c r="K30" s="38">
+        <f>K18</f>
+        <v>1.4777359748421692</v>
+      </c>
+      <c r="L30" s="38">
+        <f>N18</f>
+        <v>1.3699237966410873</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>15</v>
+      </c>
+      <c r="B31" s="38">
+        <f t="shared" ref="B31:B38" si="32">D19</f>
+        <v>1.057322248715723</v>
+      </c>
+      <c r="C31" s="38">
+        <f t="shared" ref="C31:C38" si="33">G19</f>
+        <v>1.0431289996112918</v>
+      </c>
+      <c r="D31" s="38">
+        <f t="shared" ref="D31:D38" si="34">J19</f>
+        <v>1.0506361829235888</v>
+      </c>
+      <c r="E31" s="38">
+        <f t="shared" ref="E31:E38" si="35">M19</f>
+        <v>1.0428829401381108</v>
+      </c>
+      <c r="H31">
+        <v>15</v>
+      </c>
+      <c r="I31" s="38">
+        <f t="shared" ref="I31:I38" si="36">E19</f>
+        <v>1.0442614408793338</v>
+      </c>
+      <c r="J31" s="38">
+        <f t="shared" ref="J31:J38" si="37">H19</f>
+        <v>1.0455611770770465</v>
+      </c>
+      <c r="K31" s="38">
+        <f t="shared" ref="K31:K38" si="38">K19</f>
+        <v>1.0553106192310762</v>
+      </c>
+      <c r="L31" s="38">
+        <f t="shared" ref="L31:L38" si="39">N19</f>
+        <v>1.0866303903396397</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>25</v>
+      </c>
+      <c r="B32" s="38">
+        <f t="shared" si="32"/>
+        <v>0.81745553532203297</v>
+      </c>
+      <c r="C32" s="38">
+        <f t="shared" si="33"/>
+        <v>0.8090816259300786</v>
+      </c>
+      <c r="D32" s="38">
+        <f t="shared" si="34"/>
+        <v>0.81018632241051147</v>
+      </c>
+      <c r="E32" s="38">
+        <f t="shared" si="35"/>
+        <v>0.77093078936995973</v>
+      </c>
+      <c r="H32">
+        <v>25</v>
+      </c>
+      <c r="I32" s="38">
+        <f t="shared" si="36"/>
+        <v>0.8317561371393577</v>
+      </c>
+      <c r="J32" s="38">
+        <f t="shared" si="37"/>
+        <v>0.8131447929905159</v>
+      </c>
+      <c r="K32" s="38">
+        <f t="shared" si="38"/>
+        <v>0.81190514677954506</v>
+      </c>
+      <c r="L32" s="38">
+        <f t="shared" si="39"/>
+        <v>0.81363616062742383</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>35</v>
+      </c>
+      <c r="B33" s="38">
+        <f t="shared" si="32"/>
+        <v>0.61251154249787765</v>
+      </c>
+      <c r="C33" s="38">
+        <f t="shared" si="33"/>
+        <v>0.59921369133224778</v>
+      </c>
+      <c r="D33" s="38">
+        <f t="shared" si="34"/>
+        <v>0.59719671169022437</v>
+      </c>
+      <c r="E33" s="38">
+        <f t="shared" si="35"/>
+        <v>0.61181217155265455</v>
+      </c>
+      <c r="H33">
+        <v>35</v>
+      </c>
+      <c r="I33" s="38">
+        <f t="shared" si="36"/>
+        <v>0.62499860742011126</v>
+      </c>
+      <c r="J33" s="38">
+        <f t="shared" si="37"/>
+        <v>0.62031677442350053</v>
+      </c>
+      <c r="K33" s="38">
+        <f t="shared" si="38"/>
+        <v>0.61925682867857468</v>
+      </c>
+      <c r="L33" s="38">
+        <f t="shared" si="39"/>
+        <v>0.6300776957885984</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>45</v>
+      </c>
+      <c r="B34" s="38">
+        <f t="shared" si="32"/>
+        <v>0.44061784711287155</v>
+      </c>
+      <c r="C34" s="38">
+        <f t="shared" si="33"/>
+        <v>0.44920887099862783</v>
+      </c>
+      <c r="D34" s="38">
+        <f t="shared" si="34"/>
+        <v>0.43206014868392073</v>
+      </c>
+      <c r="E34" s="38">
+        <f t="shared" si="35"/>
+        <v>0.46672279614042755</v>
+      </c>
+      <c r="H34">
+        <v>45</v>
+      </c>
+      <c r="I34" s="38">
+        <f t="shared" si="36"/>
+        <v>0.45892271293023956</v>
+      </c>
+      <c r="J34" s="38">
+        <f t="shared" si="37"/>
+        <v>0.46555838612589129</v>
+      </c>
+      <c r="K34" s="38">
+        <f t="shared" si="38"/>
+        <v>0.45112833589275059</v>
+      </c>
+      <c r="L34" s="38">
+        <f t="shared" si="39"/>
+        <v>0.47771272565851974</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>55</v>
+      </c>
+      <c r="B35" s="38">
+        <f t="shared" si="32"/>
+        <v>0.3050895850621218</v>
+      </c>
+      <c r="C35" s="38">
+        <f t="shared" si="33"/>
+        <v>0.30710807716231581</v>
+      </c>
+      <c r="D35" s="38">
+        <f t="shared" si="34"/>
+        <v>0.29324609655844214</v>
+      </c>
+      <c r="E35" s="38">
+        <f t="shared" si="35"/>
+        <v>0.32634264142568747</v>
+      </c>
+      <c r="H35">
+        <v>55</v>
+      </c>
+      <c r="I35" s="38">
+        <f t="shared" si="36"/>
+        <v>0.33448416135337755</v>
+      </c>
+      <c r="J35" s="38">
+        <f t="shared" si="37"/>
+        <v>0.33620616412817772</v>
+      </c>
+      <c r="K35" s="38">
+        <f t="shared" si="38"/>
+        <v>0.32576641209841051</v>
+      </c>
+      <c r="L35" s="38">
+        <f t="shared" si="39"/>
+        <v>0.34648610606953911</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>65</v>
+      </c>
+      <c r="B36" s="38">
+        <f t="shared" si="32"/>
+        <v>0.18476749963633771</v>
+      </c>
+      <c r="C36" s="38">
+        <f t="shared" si="33"/>
+        <v>0.18299072280205625</v>
+      </c>
+      <c r="D36" s="38">
+        <f t="shared" si="34"/>
+        <v>0.17432365614743511</v>
+      </c>
+      <c r="E36" s="38">
+        <f t="shared" si="35"/>
+        <v>0.21408399642337211</v>
+      </c>
+      <c r="H36">
+        <v>65</v>
+      </c>
+      <c r="I36" s="38">
+        <f t="shared" si="36"/>
+        <v>0.2013734179894584</v>
+      </c>
+      <c r="J36" s="38">
+        <f t="shared" si="37"/>
+        <v>0.20716355868869901</v>
+      </c>
+      <c r="K36" s="38">
+        <f t="shared" si="38"/>
+        <v>0.20603969658886986</v>
+      </c>
+      <c r="L36" s="38">
+        <f t="shared" si="39"/>
+        <v>0.22835706957034593</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>75</v>
+      </c>
+      <c r="B37" s="38">
+        <f t="shared" si="32"/>
+        <v>6.424886150625897E-2</v>
+      </c>
+      <c r="C37" s="38">
+        <f t="shared" si="33"/>
+        <v>7.3068774054895452E-2</v>
+      </c>
+      <c r="D37" s="38">
+        <f t="shared" si="34"/>
+        <v>6.9212560531936196E-2</v>
+      </c>
+      <c r="E37" s="38">
+        <f t="shared" si="35"/>
+        <v>9.387090287589285E-2</v>
+      </c>
+      <c r="H37">
+        <v>75</v>
+      </c>
+      <c r="I37" s="38">
+        <f t="shared" si="36"/>
+        <v>7.2271713185201023E-2</v>
+      </c>
+      <c r="J37" s="38">
+        <f t="shared" si="37"/>
+        <v>8.2971368098723949E-2</v>
+      </c>
+      <c r="K37" s="38">
+        <f t="shared" si="38"/>
+        <v>8.4909131441002123E-2</v>
+      </c>
+      <c r="L37" s="38">
+        <f t="shared" si="39"/>
+        <v>0.10298551382201149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>90</v>
+      </c>
+      <c r="B38" s="38">
+        <f t="shared" si="32"/>
+        <v>1.1937990566106801E-2</v>
+      </c>
+      <c r="C38" s="38">
+        <f t="shared" si="33"/>
+        <v>1.3128622495389134E-2</v>
+      </c>
+      <c r="D38" s="38">
+        <f t="shared" si="34"/>
+        <v>1.2987920289866556E-2</v>
+      </c>
+      <c r="E38" s="38">
+        <f t="shared" si="35"/>
+        <v>3.098001675978369E-2</v>
+      </c>
+      <c r="H38">
+        <v>90</v>
+      </c>
+      <c r="I38" s="38">
+        <f t="shared" si="36"/>
+        <v>1.4318904295862269E-2</v>
+      </c>
+      <c r="J38" s="38">
+        <f t="shared" si="37"/>
+        <v>1.6345846684630298E-2</v>
+      </c>
+      <c r="K38" s="38">
+        <f t="shared" si="38"/>
+        <v>1.6880532527843238E-2</v>
+      </c>
+      <c r="L38" s="38">
+        <f t="shared" si="39"/>
+        <v>3.3681213651080892E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -27518,10 +33986,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="I2" s="29"/>
+      <c r="I2" s="30"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -29555,16 +36023,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="30"/>
+      <c r="C1" s="31"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="30"/>
+      <c r="I1" s="31"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -29577,20 +36045,20 @@
         <v>1</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="30"/>
+      <c r="F3" s="31"/>
       <c r="H3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="30" t="s">
+      <c r="K3" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="30"/>
+      <c r="L3" s="31"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
@@ -32889,40 +39357,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="K1" s="31" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="K1" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="30"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="H2" s="30" t="s">
+      <c r="F2" s="31"/>
+      <c r="H2" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="30"/>
+      <c r="I2" s="31"/>
       <c r="K2" s="5" t="s">
         <v>77</v>
       </c>
@@ -37886,16 +44354,16 @@
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B1" s="6"/>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
       <c r="M1" s="15"/>
       <c r="N1" s="15"/>
       <c r="O1" s="15"/>
@@ -37911,109 +44379,109 @@
       <c r="W1" s="25"/>
       <c r="X1" s="25"/>
       <c r="Y1" s="25"/>
-      <c r="AA1" s="32" t="s">
+      <c r="AA1" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AJ1" s="32" t="s">
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33"/>
+      <c r="AJ1" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="32"/>
+      <c r="AK1" s="33"/>
+      <c r="AL1" s="33"/>
+      <c r="AM1" s="33"/>
+      <c r="AN1" s="33"/>
+      <c r="AO1" s="33"/>
+      <c r="AP1" s="33"/>
+      <c r="AQ1" s="33"/>
       <c r="AR1" s="6"/>
       <c r="AS1" s="6"/>
-      <c r="AU1" s="32" t="s">
+      <c r="AU1" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="AV1" s="32"/>
-      <c r="AW1" s="32"/>
-      <c r="AX1" s="32"/>
-      <c r="AY1" s="32"/>
-      <c r="AZ1" s="32"/>
-      <c r="BA1" s="32"/>
-      <c r="BB1" s="32"/>
+      <c r="AV1" s="33"/>
+      <c r="AW1" s="33"/>
+      <c r="AX1" s="33"/>
+      <c r="AY1" s="33"/>
+      <c r="AZ1" s="33"/>
+      <c r="BA1" s="33"/>
+      <c r="BB1" s="33"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="F2" s="32" t="s">
+      <c r="D2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="I2" s="32" t="s">
+      <c r="G2" s="33"/>
+      <c r="I2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="M2" s="32" t="s">
+      <c r="J2" s="33"/>
+      <c r="M2" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="N2" s="32"/>
+      <c r="N2" s="33"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="32" t="s">
+      <c r="R2" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="S2" s="32"/>
-      <c r="U2" s="32" t="s">
+      <c r="S2" s="33"/>
+      <c r="U2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="V2" s="32"/>
-      <c r="X2" s="32" t="s">
+      <c r="V2" s="33"/>
+      <c r="X2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="Y2" s="32"/>
-      <c r="AA2" s="32" t="s">
+      <c r="Y2" s="33"/>
+      <c r="AA2" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="AB2" s="32"/>
-      <c r="AD2" s="32" t="s">
+      <c r="AB2" s="33"/>
+      <c r="AD2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="AE2" s="32"/>
-      <c r="AG2" s="32" t="s">
+      <c r="AE2" s="33"/>
+      <c r="AG2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="AH2" s="32"/>
-      <c r="AJ2" s="32" t="s">
+      <c r="AH2" s="33"/>
+      <c r="AJ2" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="AK2" s="32"/>
-      <c r="AM2" s="32" t="s">
+      <c r="AK2" s="33"/>
+      <c r="AM2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="AN2" s="32"/>
-      <c r="AP2" s="32" t="s">
+      <c r="AN2" s="33"/>
+      <c r="AP2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="AQ2" s="32"/>
+      <c r="AQ2" s="33"/>
       <c r="AR2" s="6"/>
       <c r="AS2" s="6"/>
-      <c r="AU2" s="32" t="s">
+      <c r="AU2" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="AV2" s="32"/>
-      <c r="AX2" s="32" t="s">
+      <c r="AV2" s="33"/>
+      <c r="AX2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="AY2" s="32"/>
-      <c r="BA2" s="32" t="s">
+      <c r="AY2" s="33"/>
+      <c r="BA2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="BB2" s="32"/>
+      <c r="BB2" s="33"/>
     </row>
     <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="O3" s="6" t="s">
@@ -43025,11 +49493,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="AU1:BB1"/>
     <mergeCell ref="AU2:AV2"/>
     <mergeCell ref="AX2:AY2"/>
@@ -43045,6 +49508,11 @@
     <mergeCell ref="AJ2:AK2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AP2:AQ2"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
